--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SANTA FE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SANTA FE.xlsx
@@ -2404,12 +2404,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>340499</t>
+          <t>195118</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>92625</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2419,17 +2419,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KEVIN ANGEL</t>
+          <t xml:space="preserve">JUAN </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t xml:space="preserve">CORTEZ </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t xml:space="preserve">SANTOS </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2439,12 +2439,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6647630712</t>
+          <t>6644131819</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>JOSE AGUIRRE</t>
+          <t>STA FE</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2454,17 +2454,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19-04-2005</t>
+          <t>27-01-2003</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ANGELEDINA1110@GMAIL.COM</t>
+          <t>CORTEZSANTOSJUAN123@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-02-2026 10:04:17</t>
+          <t>05-09-2023 11:07:25</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-02-2026 10:21:32</t>
+          <t>03-02-2026 13:11:41</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>03-02-2026 10:09:27</t>
+          <t>03-02-2026 13:11:01</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26130522035930001999</t>
+          <t>26130522039180002014</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2539,12 +2539,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>195118</t>
+          <t>234468</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>92625</t>
+          <t>31973</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2554,17 +2554,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN </t>
+          <t xml:space="preserve">ELIZABETH </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORTEZ </t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTOS </t>
+          <t>MONCAYO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2574,32 +2574,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6644131819</t>
+          <t>6631007577</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>STA FE</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>27-01-2003</t>
+          <t>03-08-2010</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CORTEZSANTOSJUAN123@GMAIL.COM</t>
+          <t>ECASTILLOMONCAYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>05-09-2023 11:07:25</t>
+          <t>13-05-2024 20:17:29</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2620,17 +2620,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-02-2026 13:11:41</t>
+          <t>09-02-2026 22:06:58</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>03-02-2026 13:11:01</t>
+          <t>09-02-2026 22:06:25</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26130522039180002014</t>
+          <t>26130522215360002518</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2674,12 +2674,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>234468</t>
+          <t>302469</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>31973</t>
+          <t>99967</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIZABETH </t>
+          <t>RENE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t xml:space="preserve">TIRADO </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MONCAYO</t>
+          <t>CASTAÑEDA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2709,75 +2709,67 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6631007577</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>SANTA FE</t>
-        </is>
-      </c>
+          <t>6693325966</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>03-08-2010</t>
+          <t>19-08-2009</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ECASTILLOMONCAYO@GMAIL.COM</t>
+          <t>G2024_1CAM_TIRADO_RENE@CBTIS278.EDU.MX</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>13-05-2024 20:17:29</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>07-07-2025 14:42:40</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>09-02-2026 22:06:58</t>
+          <t>04-02-2026 16:57:05</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>09-02-2026 22:06:25</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2785,14 +2777,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26130522215360002518</t>
+          <t>26130522080890002128</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2809,12 +2801,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>302469</t>
+          <t>340499</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>99967</t>
+          <t>18317</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2824,17 +2816,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>RENE</t>
+          <t>KEVIN ANGEL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">TIRADO </t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CASTAÑEDA</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2844,10 +2836,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6693325966</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>6647630712</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>JOSE AGUIRRE</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2855,56 +2851,60 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>19-08-2009</t>
+          <t>19-04-2005</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>G2024_1CAM_TIRADO_RENE@CBTIS278.EDU.MX</t>
+          <t>ANGELEDINA1110@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>07-07-2025 14:42:40</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 10:04:17</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>04-02-2026 16:57:05</t>
+          <t>03-02-2026 10:21:32</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>03-02-2026 10:09:27</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2912,14 +2912,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26130522080890002128</t>
+          <t>26130522035930001999</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3758,12 +3758,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>341158</t>
+          <t>312525</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18976</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3773,17 +3773,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>LITZY MONTSERRAT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>ISAAC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ARMENTA</t>
+          <t>TEJEDA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3793,75 +3793,67 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6683205923</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>SANTA FE</t>
-        </is>
-      </c>
+          <t>3781008929</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>09-09-1991</t>
+          <t>11-05-2000</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>6683205923@GMAIL.COM</t>
+          <t>MONSERRATEJEDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>04-02-2026 19:06:27</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>02-09-2025 18:55:18</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>04-02-2026 19:10:24</t>
+          <t>03-02-2026 21:50:09</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>04-02-2026 19:09:37</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3869,14 +3861,22 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26130522087380002152</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26130522059270002082</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>LILIANA  RAMIREZ  CAMPUZANO</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3893,12 +3893,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>342063</t>
+          <t>318850</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19881</t>
+          <t>16347</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3908,27 +3908,27 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIELA </t>
+          <t>RAFAEL ALEJANDRO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TEZETA</t>
+          <t>CASTELLANOS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6648422648</t>
+          <t>6199225203</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3938,22 +3938,22 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>19-07-1991</t>
+          <t>15-10-1995</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>6648422648@GMAIL.COM</t>
+          <t>ALEJANDRO.AGUILARCAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>09-02-2026 08:58:54</t>
+          <t>15-10-2025 08:38:09</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3974,17 +3974,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>10-02-2026 19:26:57</t>
+          <t>02-02-2026 19:13:04</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>10-02-2026 19:26:34</t>
+          <t>02-02-2026 19:12:24</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26130522246820002603</t>
+          <t>26130522021820001963</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>Yessica Angulo Barragan</t>
+          <t>ERIKA  RUIZ GONZALEZ</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4024,24 +4024,24 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Irving Correa Franco</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>340241</t>
+          <t>341158</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18059</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4051,17 +4051,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>HECTOR EFRAIN</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CEDANO</t>
+          <t>ARMENTA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6646703061</t>
+          <t>6683205923</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4086,17 +4086,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>08-08-1983</t>
+          <t>09-09-1991</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>HDIAZ@EDUBC.MX</t>
+          <t>6683205923@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>02-02-2026 15:59:13</t>
+          <t>04-02-2026 19:06:27</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4117,17 +4117,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>02-02-2026 20:14:53</t>
+          <t>04-02-2026 19:10:24</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>02-02-2026 20:13:31</t>
+          <t>04-02-2026 19:09:37</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26130522022910001972</t>
+          <t>26130522087380002152</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4159,24 +4159,24 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Luis Enrique  Silva Reyna</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>340432</t>
+          <t>342063</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18250</t>
+          <t>19881</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4186,17 +4186,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MIREYA</t>
+          <t xml:space="preserve">MARIELA </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ELISEA</t>
+          <t>TEZETA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6633192222</t>
+          <t>6648422648</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4221,17 +4221,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>25-07-2005</t>
+          <t>19-07-1991</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>MIREYAELISEA18@GMAIL.COM</t>
+          <t>6648422648@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>03-02-2026 06:29:36</t>
+          <t>09-02-2026 08:58:54</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4252,17 +4252,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>04-02-2026 07:46:58</t>
+          <t>10-02-2026 19:26:57</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>04-02-2026 07:46:19</t>
+          <t>10-02-2026 19:26:34</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26130522068680002095</t>
+          <t>26130522246820002603</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>ERIKA  RUIZ GONZALEZ</t>
+          <t>Yessica Angulo Barragan</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4302,24 +4302,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Irving Correa Franco</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>312525</t>
+          <t>340241</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>18059</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4329,17 +4329,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LITZY MONTSERRAT</t>
+          <t>HECTOR EFRAIN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ISAAC</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TEJEDA</t>
+          <t>CEDANO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4349,67 +4349,75 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3781008929</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6646703061</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>11-05-2000</t>
+          <t>08-08-1983</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>MONSERRATEJEDA@GMAIL.COM</t>
+          <t>HDIAZ@EDUBC.MX</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>02-09-2025 18:55:18</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 15:59:13</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>03-02-2026 21:50:09</t>
+          <t>02-02-2026 20:14:53</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>02-02-2026 20:13:31</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4417,44 +4425,36 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26130522059270002082</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>LILIANA  RAMIREZ  CAMPUZANO</t>
-        </is>
-      </c>
+          <t>26130522022910001972</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Enrique  Silva Reyna</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>318850</t>
+          <t>340432</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16347</t>
+          <t>18250</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4464,52 +4464,52 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>RAFAEL ALEJANDRO</t>
+          <t>MIREYA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CASTELLANOS</t>
+          <t>ELISEA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6199225203</t>
+          <t>6633192222</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>VILLA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>15-10-1995</t>
+          <t>25-07-2005</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ALEJANDRO.AGUILARCAS@GMAIL.COM</t>
+          <t>MIREYAELISEA18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>15-10-2025 08:38:09</t>
+          <t>03-02-2026 06:29:36</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4530,17 +4530,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>02-02-2026 19:13:04</t>
+          <t>04-02-2026 07:46:58</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>02-02-2026 19:12:24</t>
+          <t>04-02-2026 07:46:19</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26130522021820001963</t>
+          <t>26130522068680002095</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -5541,12 +5541,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>339953</t>
+          <t>340345</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17771</t>
+          <t>18163</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5556,17 +5556,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KEVIN ALEXANDER</t>
+          <t>DIEGO ARMANDO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>GUERRERO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>QUIROA</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5576,14 +5576,10 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6647707013</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>RINA</t>
-        </is>
-      </c>
+          <t>6645534808</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5591,38 +5587,42 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>21-04-2004</t>
+          <t>29-12-2007</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>KEVINALEXANDERAGUILAR@GMAIL.COM</t>
+          <t>6645534808@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>02-02-2026 09:21:11</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>02-02-2026 18:34:52</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>02-02-2026 09:25:05</t>
+          <t>02-02-2026 18:36:06</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -5630,21 +5630,13 @@
           <t>02-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>02-02-2026 09:24:33</t>
-        </is>
-      </c>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5652,14 +5644,14 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26130522002920001887</t>
+          <t>26130522020760001960</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5676,12 +5668,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>340345</t>
+          <t>339953</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>17771</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5691,17 +5683,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DIEGO ARMANDO</t>
+          <t>KEVIN ALEXANDER</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>QUIROA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5711,10 +5703,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6645534808</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>6647707013</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>RINA</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5722,42 +5718,38 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>29-12-2007</t>
+          <t>21-04-2004</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>6645534808@GMAIL.COM</t>
+          <t>KEVINALEXANDERAGUILAR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>02-02-2026 18:34:52</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 09:21:11</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>02-02-2026 18:36:06</t>
+          <t>02-02-2026 09:25:05</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5765,13 +5757,21 @@
           <t>02-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr"/>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>02-02-2026 09:24:33</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5779,14 +5779,14 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26130522020760001960</t>
+          <t>26130522002920001887</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -6347,12 +6347,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>340309</t>
+          <t>343352</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>21169</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6362,17 +6362,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>GERMAN FERNANDO</t>
+          <t>ARMANDO JOCIEL</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>WATANABE</t>
+          <t xml:space="preserve">MOJICA </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6382,32 +6382,32 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6647500296</t>
+          <t>6641561536</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>STA FE</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>09-04-1972</t>
+          <t>28-05-1995</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>6641232927@GMAIL.COM</t>
+          <t>JOCYTECH2026@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>02-02-2026 17:26:36</t>
+          <t>12-02-2026 17:53:49</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6428,17 +6428,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>04-02-2026 16:31:00</t>
+          <t>12-02-2026 17:58:01</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>04-02-2026 16:29:50</t>
+          <t>12-02-2026 17:57:26</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6458,19 +6458,11 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26130522079790002126</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>MARIA CANDELARIA LARA AVILA</t>
-        </is>
-      </c>
+          <t>26130522301250002720</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
           <t>499</t>
@@ -6478,24 +6470,24 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Edgar Joshua O´Gam  Espinosa Sanchez</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>340348</t>
+          <t>340309</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>18127</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6505,17 +6497,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ALFONSO YAREL</t>
+          <t>GERMAN FERNANDO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>WATANABE</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6525,10 +6517,14 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6631024759</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>6647500296</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6536,56 +6532,60 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>05-07-2008</t>
+          <t>09-04-1972</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>6631024759@GMAIL.COM</t>
+          <t>6641232927@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>02-02-2026 18:37:22</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 17:26:36</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>02-02-2026 18:38:01</t>
+          <t>04-02-2026 16:31:00</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>04-02-2026 16:29:50</t>
+        </is>
+      </c>
       <c r="U46" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6593,14 +6593,22 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26130522020860001961</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
+          <t>26130522079790002126</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>MARIA CANDELARIA LARA AVILA</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -6617,12 +6625,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>343352</t>
+          <t>340348</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>18166</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6632,17 +6640,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ARMANDO JOCIEL</t>
+          <t>ALFONSO YAREL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOJICA </t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6652,75 +6660,67 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6641561536</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>STA FE</t>
-        </is>
-      </c>
+          <t>6631024759</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>28-05-1995</t>
+          <t>05-07-2008</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>JOCYTECH2026@GMAIL.COM</t>
+          <t>6631024759@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>12-02-2026 17:53:49</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>02-02-2026 18:37:22</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>12-02-2026 17:58:01</t>
+          <t>02-02-2026 18:38:01</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>12-02-2026 17:57:26</t>
-        </is>
-      </c>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6728,24 +6728,24 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26130522301250002720</t>
+          <t>26130522020860001961</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Edgar Joshua O´Gam  Espinosa Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -7026,12 +7026,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>340383</t>
+          <t>340770</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18201</t>
+          <t>18588</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7041,17 +7041,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>IKER</t>
+          <t>ENRIQUE ISAI</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>BON</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BENITEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3251030954</t>
+          <t>6682513296</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -7076,48 +7076,52 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>24-02-2013</t>
+          <t>31-01-1992</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>6646703061@GMAIL.COM</t>
+          <t>6682513296@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>02-02-2026 20:16:41</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>03-02-2026 18:07:24</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>02-02-2026 20:19:16</t>
+          <t>03-02-2026 18:09:33</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>02-02-2026 20:18:33</t>
+          <t>03-02-2026 18:08:59</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7137,14 +7141,14 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26130522022970001973</t>
+          <t>26130522052080002057</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -7161,12 +7165,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>340491</t>
+          <t>340233</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18309</t>
+          <t>18051</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7176,17 +7180,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AARON ALDAIR</t>
+          <t>VICTOR RAMON</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESPINOZA </t>
+          <t>ESPARZA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7196,75 +7200,67 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6611033672</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>SANTA FE</t>
-        </is>
-      </c>
+          <t>6647614728</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>01-07-1999</t>
+          <t>12-11-2009</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>6611033672@GMAIL.COM</t>
+          <t>6647614728@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>03-02-2026 09:29:00</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>02-02-2026 15:52:42</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>03-02-2026 09:32:47</t>
+          <t>02-02-2026 15:54:28</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>03-02-2026 09:32:24</t>
-        </is>
-      </c>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7272,36 +7268,36 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26130522035180001998</t>
+          <t>26130522015360001934</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Jose Alfredo Andraca Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>340233</t>
+          <t>340383</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>18051</t>
+          <t>18201</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7311,17 +7307,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VICTOR RAMON</t>
+          <t>IKER</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ESPARZA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>BENITEZ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7331,10 +7327,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6647614728</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>3251030954</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7342,42 +7342,38 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>12-11-2009</t>
+          <t>24-02-2013</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>6647614728@GMAIL.COM</t>
+          <t>6646703061@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>02-02-2026 15:52:42</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 20:16:41</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>02-02-2026 15:54:28</t>
+          <t>02-02-2026 20:19:16</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -7385,13 +7381,21 @@
           <t>02-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr"/>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>02-02-2026 20:18:33</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7399,14 +7403,14 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26130522015360001934</t>
+          <t>26130522022970001973</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7423,12 +7427,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>343440</t>
+          <t>340491</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21257</t>
+          <t>18309</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7438,17 +7442,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t>AARON ALDAIR</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t xml:space="preserve">ESPINOZA </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CULEBRO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7458,32 +7462,32 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6644080703</t>
+          <t>6611033672</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>DELICIAS</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>25-08-2000</t>
+          <t>01-07-1999</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>SOLISCULEBROJOSE@HOTMAIL.COM</t>
+          <t>6611033672@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>13-02-2026 08:49:01</t>
+          <t>03-02-2026 09:29:00</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -7504,17 +7508,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>13-02-2026 08:57:01</t>
+          <t>03-02-2026 09:32:47</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>13-02-2026 08:56:19</t>
+          <t>03-02-2026 09:32:24</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7534,7 +7538,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26130522316950002767</t>
+          <t>26130522035180001998</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
@@ -7828,12 +7832,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>340770</t>
+          <t>343440</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>18588</t>
+          <t>21257</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7843,17 +7847,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ENRIQUE ISAI</t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BON</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>CULEBRO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7863,12 +7867,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6682513296</t>
+          <t>6644080703</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>DELICIAS</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7878,52 +7882,48 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>31-01-1992</t>
+          <t>25-08-2000</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>6682513296@GMAIL.COM</t>
+          <t>SOLISCULEBROJOSE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>03-02-2026 18:07:24</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-02-2026 08:49:01</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>03-02-2026 18:09:33</t>
+          <t>13-02-2026 08:57:01</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>03-02-2026 18:08:59</t>
+          <t>13-02-2026 08:56:19</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7943,24 +7943,24 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26130522052080002057</t>
+          <t>26130522316950002767</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Alfredo Andraca Rodriguez</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -8237,12 +8237,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>341255</t>
+          <t>341174</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>18992</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8252,17 +8252,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIELA ABRIL </t>
+          <t xml:space="preserve">ISABELLA </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESPINOZA </t>
+          <t>CASTRUITA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PRIETO</t>
+          <t xml:space="preserve"> FRANCO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8272,14 +8272,10 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6641237911</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTA FE </t>
-        </is>
-      </c>
+          <t>6645837560</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8287,60 +8283,56 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>05-04-1991</t>
+          <t>09-09-2008</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>DANYUVITA@HOTMAIL.COM</t>
+          <t>ISABELLACASTRUITAFRANCO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>05-02-2026 09:42:06</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>04-02-2026 19:33:20</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>05-02-2026 09:56:39</t>
+          <t>04-02-2026 19:36:39</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>05-02-2026 09:55:53</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8348,14 +8340,14 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26130522102170002203</t>
+          <t>26130522088310002158</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
@@ -8372,12 +8364,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>341368</t>
+          <t>341255</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>19186</t>
+          <t>19073</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8387,17 +8379,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ALLISON</t>
+          <t xml:space="preserve">DANIELA ABRIL </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t xml:space="preserve">ESPINOZA </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>PRIETO</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8407,10 +8399,14 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>4424748485</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>6641237911</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTA FE </t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8418,42 +8414,38 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>28-08-2009</t>
+          <t>05-04-1991</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>4424748485@GMAIL.COM</t>
+          <t>DANYUVITA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>05-02-2026 16:31:44</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 09:42:06</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>05-02-2026 16:32:46</t>
+          <t>05-02-2026 09:56:39</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -8461,13 +8453,21 @@
           <t>05-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr"/>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>05-02-2026 09:55:53</t>
+        </is>
+      </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W60" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8475,14 +8475,14 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26130522110550002235</t>
+          <t>26130522102170002203</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
@@ -8499,12 +8499,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>343928</t>
+          <t>341368</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>19186</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8514,19 +8514,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CLAUDIA LIZETH</t>
+          <t>ALLISON</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>HERNANDEZ</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>ROBLES</t>
-        </is>
-      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>52</t>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6647583802</t>
+          <t>4424748485</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8545,17 +8545,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>26-03-1983</t>
+          <t>28-08-2009</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLAUDIALIZETHHERNANDEZ@GMAIL.COM</t>
+          <t>4424748485@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>16-02-2026 06:29:48</t>
+          <t>05-02-2026 16:31:44</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8570,22 +8570,22 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>18-02-2026 06:39:41</t>
+          <t>05-02-2026 16:32:46</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -8602,22 +8602,14 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26130522455610003067</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>ERIKA  RUIZ GONZALEZ</t>
-        </is>
-      </c>
+          <t>26130522110550002235</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
@@ -8634,12 +8626,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>340687</t>
+          <t>343928</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8649,17 +8641,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>YOLANDA</t>
+          <t>CLAUDIA LIZETH</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARCE </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8669,14 +8661,10 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6642833034</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>SANTA FE</t>
-        </is>
-      </c>
+          <t>6647583802</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8684,60 +8672,56 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>04-02-1966</t>
+          <t>26-03-1983</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>YOLANDAARCEBELTRAN0216@GMAIL.COM</t>
+          <t>CLAUDIALIZETHHERNANDEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>03-02-2026 16:52:29</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>16-02-2026 06:29:48</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>03-02-2026 17:10:43</t>
+          <t>18-02-2026 06:39:41</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>03-02-2026 17:01:48</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8745,14 +8729,22 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26130522048270002040</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
+          <t>26130522455610003067</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>ERIKA  RUIZ GONZALEZ</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
@@ -8769,12 +8761,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>340747</t>
+          <t>340687</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>18505</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8784,17 +8776,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>YADIRA ZULAMIT</t>
+          <t>YOLANDA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t xml:space="preserve"> ARCE </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8804,10 +8796,14 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6634633015</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>6642833034</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8815,42 +8811,38 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>29-11-1985</t>
+          <t>04-02-1966</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>6634633015@GMAIL.COM</t>
+          <t>YOLANDAARCEBELTRAN0216@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>03-02-2026 17:45:45</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 16:52:29</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>03-02-2026 17:49:38</t>
+          <t>03-02-2026 17:10:43</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -8858,13 +8850,21 @@
           <t>03-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr"/>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>03-02-2026 17:01:48</t>
+        </is>
+      </c>
       <c r="U63" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr"/>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W63" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8872,36 +8872,36 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26130522050920002051</t>
+          <t>26130522048270002040</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Luis Enrique  Silva Reyna</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>341174</t>
+          <t>340747</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>18992</t>
+          <t>18565</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8911,17 +8911,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISABELLA </t>
+          <t>YADIRA ZULAMIT</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CASTRUITA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> FRANCO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6645837560</t>
+          <t>6634633015</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8942,17 +8942,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>09-09-2008</t>
+          <t>29-11-1985</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>ISABELLACASTRUITAFRANCO@GMAIL.COM</t>
+          <t>6634633015@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>04-02-2026 19:33:20</t>
+          <t>03-02-2026 17:45:45</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -8967,22 +8967,22 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>04-02-2026 19:36:39</t>
+          <t>03-02-2026 17:49:38</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -8999,24 +8999,24 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26130522088310002158</t>
+          <t>26130522050920002051</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Enrique  Silva Reyna</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -9444,12 +9444,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>342037</t>
+          <t>340991</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19855</t>
+          <t>18809</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9459,17 +9459,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AMERICA GUADALUPE</t>
+          <t>LENYS STEFANY</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ANGULO</t>
+          <t>PULIDO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>CORREA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6641216014</t>
+          <t>5549118448</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>STA FE</t>
+          <t>PRADERAS</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9494,48 +9494,52 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>11-12-1993</t>
+          <t>21-06-1995</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>AMERICA.ANG.RDZ.1@GMAIL.COM</t>
+          <t>LENYSPULIDO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>09-02-2026 07:29:48</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>04-02-2026 13:39:18</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>09-02-2026 07:40:19</t>
+          <t>04-02-2026 13:58:04</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>09-02-2026 07:39:38</t>
+          <t>04-02-2026 13:57:15</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -9545,7 +9549,7 @@
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -9555,36 +9559,36 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26130522183590002407</t>
+          <t>26130522075170002113</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>Jose Alfredo Andraca Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>340991</t>
+          <t>342037</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>18809</t>
+          <t>19855</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9594,17 +9598,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LENYS STEFANY</t>
+          <t>AMERICA GUADALUPE</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PULIDO</t>
+          <t>ANGULO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CORREA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9614,12 +9618,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>5549118448</t>
+          <t>6641216014</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>PRADERAS</t>
+          <t>STA FE</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9629,52 +9633,48 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>21-06-1995</t>
+          <t>11-12-1993</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>LENYSPULIDO@GMAIL.COM</t>
+          <t>AMERICA.ANG.RDZ.1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>04-02-2026 13:39:18</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 07:29:48</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>04-02-2026 13:58:04</t>
+          <t>09-02-2026 07:40:19</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>04-02-2026 13:57:15</t>
+          <t>09-02-2026 07:39:38</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -9684,7 +9684,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -9694,36 +9694,36 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26130522075170002113</t>
+          <t>26130522183590002407</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Alfredo Andraca Rodriguez</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>342353</t>
+          <t>342062</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>20171</t>
+          <t>19880</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9733,17 +9733,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LITZY THAMARA</t>
+          <t>MARIA MAGDALENA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>IBARRA</t>
+          <t>TEZETA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9753,10 +9753,14 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6631023763</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>6644151317</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>URBI</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9764,42 +9768,38 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>12-09-2001</t>
+          <t>09-05-1994</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>6631023763@GMAIL.COM</t>
+          <t>CASTILLEJOSANTHONI43@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>09-02-2026 17:49:19</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 08:58:46</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>09-02-2026 17:51:13</t>
+          <t>09-02-2026 09:03:22</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -9807,13 +9807,21 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr"/>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>09-02-2026 09:01:30</t>
+        </is>
+      </c>
       <c r="U70" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr"/>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W70" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9821,36 +9829,36 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26130522204230002469</t>
+          <t>26130522185750002415</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Irving Correa Franco</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>341895</t>
+          <t>341909</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>19713</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9860,17 +9868,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>JOHANNA ANGELICA</t>
+          <t>BLANCA ESTELA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CLEMENTE</t>
+          <t>ACEVES</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9880,12 +9888,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6647975390</t>
+          <t>6737398901</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>LOMAS</t>
+          <t>SIENA SARACINI</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9895,17 +9903,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>10-09-1995</t>
+          <t>23-07-1987</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>JOHANNAT824@GMAIL.COM</t>
+          <t>BLANCAESTELAPARRA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>08-02-2026 10:09:21</t>
+          <t>08-02-2026 11:06:13</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9926,17 +9934,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>12-02-2026 21:25:37</t>
+          <t>08-02-2026 11:11:37</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>12-02-2026 21:24:54</t>
+          <t>08-02-2026 11:10:52</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -9946,7 +9954,7 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -9956,19 +9964,11 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26130522307000002750</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>ERIKA  RUIZ GONZALEZ</t>
-        </is>
-      </c>
+          <t>26130522170280002379</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr">
         <is>
           <t>499</t>
@@ -9976,24 +9976,24 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>Luis Enrique  Silva Reyna</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>341909</t>
+          <t>342353</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>19727</t>
+          <t>20171</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10003,17 +10003,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BLANCA ESTELA</t>
+          <t>LITZY THAMARA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ACEVES</t>
+          <t>IBARRA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -10023,14 +10023,10 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>6737398901</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>SIENA SARACINI</t>
-        </is>
-      </c>
+          <t>6631023763</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -10038,60 +10034,56 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>23-07-1987</t>
+          <t>12-09-2001</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>BLANCAESTELAPARRA@GMAIL.COM</t>
+          <t>6631023763@GMAIL.COM</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>08-02-2026 11:06:13</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>09-02-2026 17:49:19</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>08-02-2026 11:11:37</t>
+          <t>09-02-2026 17:51:13</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>08-02-2026 11:10:52</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10099,14 +10091,14 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>26130522170280002379</t>
+          <t>26130522204230002469</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
@@ -10123,12 +10115,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>342062</t>
+          <t>341895</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>19713</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10138,17 +10130,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>MARIA MAGDALENA</t>
+          <t>JOHANNA ANGELICA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>TEZETA</t>
+          <t>CLEMENTE</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10158,12 +10150,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6644151317</t>
+          <t>6647975390</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>URBI</t>
+          <t>LOMAS</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -10173,17 +10165,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>09-05-1994</t>
+          <t>10-09-1995</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CASTILLEJOSANTHONI43@GMAIL.COM</t>
+          <t>JOHANNAT824@GMAIL.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>09-02-2026 08:58:46</t>
+          <t>08-02-2026 10:09:21</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -10204,17 +10196,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>09-02-2026 09:03:22</t>
+          <t>12-02-2026 21:25:37</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>09-02-2026 09:01:30</t>
+          <t>12-02-2026 21:24:54</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -10234,11 +10226,19 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26130522185750002415</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
+          <t>26130522307000002750</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>ERIKA  RUIZ GONZALEZ</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>499</t>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Irving Correa Franco</t>
+          <t>Luis Enrique  Silva Reyna</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -10258,12 +10258,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>342995</t>
+          <t>342318</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>20812</t>
+          <t>20136</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10273,34 +10273,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t xml:space="preserve">MARCO ANTONIO </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>ZAMORA</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6644836786</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>SANTA FE</t>
-        </is>
-      </c>
+          <t>2397100283</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -10308,60 +10304,56 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>21-10-2008</t>
+          <t>10-06-1992</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>6644836786@GMAIL.COM</t>
+          <t>GEMINISMILIE22@GMAIL.COM</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>11-02-2026 14:52:15</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>09-02-2026 17:20:45</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>11-02-2026 14:54:19</t>
+          <t>09-02-2026 17:22:46</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>11-02-2026 14:53:52</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10369,14 +10361,14 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26130522265640002639</t>
+          <t>26130522201980002460</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
@@ -10393,12 +10385,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>341674</t>
+          <t>345863</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>88028</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10408,17 +10400,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>KARINA</t>
+          <t>MONICA LETICIA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>OLIVEROS</t>
+          <t xml:space="preserve"> CORNEJO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t xml:space="preserve"> DE LUNA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -10428,7 +10420,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>6633246353</t>
+          <t>6645675605</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -10443,48 +10435,52 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>20-04-1999</t>
+          <t>10-04-1985</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>KAREL16DEFEBRERO@GMAIL.COM</t>
+          <t>MONI.CORNEJOLUNA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>06-02-2026 18:46:47</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+          <t>23-02-2026 16:18:44</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>06-02-2026 18:58:32</t>
+          <t>23-02-2026 16:28:00</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>06-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>06-02-2026 18:57:00</t>
+          <t>23-02-2026 16:25:44</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -10494,7 +10490,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -10504,14 +10500,14 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>26130522145960002320</t>
+          <t>26130522587120003348</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
@@ -10528,12 +10524,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>345863</t>
+          <t>341674</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>88028</t>
+          <t>19492</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10543,17 +10539,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>MONICA LETICIA</t>
+          <t>KARINA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CORNEJO</t>
+          <t>OLIVEROS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DE LUNA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -10563,7 +10559,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>6645675605</t>
+          <t>6633246353</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -10578,52 +10574,48 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>10-04-1985</t>
+          <t>20-04-1999</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>MONI.CORNEJOLUNA@GMAIL.COM</t>
+          <t>KAREL16DEFEBRERO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>23-02-2026 16:18:44</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>06-02-2026 18:46:47</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>23-02-2026 16:28:00</t>
+          <t>06-02-2026 18:58:32</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>06-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>23-02-2026 16:25:44</t>
+          <t>06-02-2026 18:57:00</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -10633,7 +10625,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -10643,14 +10635,14 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>26130522587120003348</t>
+          <t>26130522145960002320</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
@@ -10667,12 +10659,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>342487</t>
+          <t>342995</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>20304</t>
+          <t>20812</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10682,17 +10674,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>BRENDA VANESSA</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MUÑOZ</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> OLVERA</t>
+          <t>ZAMORA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -10702,67 +10694,75 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>3111166926</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>6644836786</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>03-03-2004</t>
+          <t>21-10-2008</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>ANESAOLVERA9@GMAIL.COM</t>
+          <t>6644836786@GMAIL.COM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>09-02-2026 20:25:38</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 14:52:15</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>17-02-2026 18:41:17</t>
+          <t>11-02-2026 14:54:19</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>11-02-2026 14:53:52</t>
+        </is>
+      </c>
       <c r="U77" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10770,32 +10770,24 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>26130522442270003041</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>Yessica Angulo Barragan</t>
-        </is>
-      </c>
+          <t>26130522265640002639</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>Irving Correa Franco</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -10949,12 +10941,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>342318</t>
+          <t>342487</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>20136</t>
+          <t>20304</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -10964,48 +10956,48 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARCO ANTONIO </t>
+          <t>BRENDA VANESSA</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t xml:space="preserve"> MUÑOZ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t xml:space="preserve"> OLVERA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2397100283</t>
+          <t>3111166926</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>10-06-1992</t>
+          <t>03-03-2004</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>GEMINISMILIE22@GMAIL.COM</t>
+          <t>ANESAOLVERA9@GMAIL.COM</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>09-02-2026 17:20:45</t>
+          <t>09-02-2026 20:25:38</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -11020,28 +11012,28 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>09-02-2026 17:22:46</t>
+          <t>17-02-2026 18:41:17</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T79" t="inlineStr"/>
       <c r="U79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V79" t="inlineStr"/>
@@ -11052,24 +11044,32 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>26130522201980002460</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="inlineStr"/>
+          <t>26130522442270003041</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>Yessica Angulo Barragan</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Irving Correa Franco</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -11473,12 +11473,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>342726</t>
+          <t>342471</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>20543</t>
+          <t>20288</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11488,17 +11488,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>DIANA PATRICIA</t>
+          <t>EDGAR RICARDO</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t xml:space="preserve"> OLIVO </t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RAFAEL</t>
+          <t>CERDA</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>6646115488</t>
+          <t>6642587482</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -11518,22 +11518,22 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>11-04-1998</t>
+          <t>30-08-1983</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>6646115488@GMAIL.COM</t>
+          <t>EDGAROLIVOCERDA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>10-02-2026 16:56:48</t>
+          <t>09-02-2026 20:01:16</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -11554,17 +11554,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>10-02-2026 17:02:36</t>
+          <t>09-02-2026 20:08:18</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>10-02-2026 17:01:48</t>
+          <t>09-02-2026 20:07:24</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>26130522238260002574</t>
+          <t>26130522213030002501</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr"/>
@@ -11596,24 +11596,24 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Enrique  Silva Reyna</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>342953</t>
+          <t>342992</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>20770</t>
+          <t>20809</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11623,87 +11623,95 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VICTOR HUGO</t>
+          <t>LUIS HECTOR</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ARIAS</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>ZAMORA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>6631084871</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>01-10-2004</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>6645974918@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>11-02-2026 14:45:11</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>11-02-2026 14:51:11</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>11-02-2026 14:50:14</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>6196460414</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>29-12-1979</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>VICTORHUGOARIAS@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>11-02-2026 12:02:44</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>Sin contrato</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>1 MES $899</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>899</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>11-02-2026 12:10:42</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -11711,14 +11719,14 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>26130522262770002628</t>
+          <t>26130522265570002638</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
@@ -11735,12 +11743,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>342471</t>
+          <t>342726</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>20288</t>
+          <t>20543</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11750,17 +11758,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EDGAR RICARDO</t>
+          <t>DIANA PATRICIA</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> OLIVO </t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CERDA</t>
+          <t>RAFAEL</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -11770,7 +11778,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>6642587482</t>
+          <t>6646115488</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -11780,22 +11788,22 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>30-08-1983</t>
+          <t>11-04-1998</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>EDGAROLIVOCERDA@HOTMAIL.COM</t>
+          <t>6646115488@GMAIL.COM</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>09-02-2026 20:01:16</t>
+          <t>10-02-2026 16:56:48</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -11816,17 +11824,17 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>09-02-2026 20:08:18</t>
+          <t>10-02-2026 17:02:36</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>09-02-2026 20:07:24</t>
+          <t>10-02-2026 17:01:48</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -11836,7 +11844,7 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -11846,7 +11854,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>26130522213030002501</t>
+          <t>26130522238260002574</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr"/>
@@ -11858,24 +11866,24 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>Luis Enrique  Silva Reyna</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>343679</t>
+          <t>342953</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>21496</t>
+          <t>20770</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -11885,27 +11893,27 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELIPE DE JESUS </t>
+          <t>VICTOR HUGO</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">NARANJO </t>
+          <t>ARIAS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BOJORQUEZ</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>6643056800</t>
+          <t>6196460414</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -11916,17 +11924,17 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>21-11-2005</t>
+          <t>29-12-1979</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>6643056800@GMAIL.COM</t>
+          <t>VICTORHUGOARIAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>14-02-2026 09:51:20</t>
+          <t>11-02-2026 12:02:44</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -11951,12 +11959,12 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>14-02-2026 09:52:12</t>
+          <t>11-02-2026 12:10:42</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T86" t="inlineStr"/>
@@ -11973,7 +11981,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>26130522345150002832</t>
+          <t>26130522262770002628</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr"/>
@@ -11997,12 +12005,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>345343</t>
+          <t>346635</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>87508</t>
+          <t>88800</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -12012,17 +12020,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>DIEGO GAEL</t>
+          <t>JHON FREDY</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>NAVARRETE</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>CASTAÑEDA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -12032,10 +12040,14 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>6631996723</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>9902932445</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>STA FE</t>
+        </is>
+      </c>
       <c r="J87" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -12043,42 +12055,42 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>11-03-2012</t>
+          <t>15-12-1991</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>DIEGOGAELNAVARRETE@GMAIL.COM</t>
+          <t>JOHNFREDYMADRID@GMAIL.COM</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>20-02-2026 16:47:40</t>
+          <t>26-02-2026 06:38:48</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>26-02-2026 18:11:50</t>
+          <t>26-02-2026 06:53:14</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -12086,13 +12098,21 @@
           <t>26-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr"/>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>26-02-2026 06:47:24</t>
+        </is>
+      </c>
       <c r="U87" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr"/>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W87" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12100,22 +12120,14 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>26130522692170003631</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>LILIANA  RAMIREZ  CAMPUZANO</t>
-        </is>
-      </c>
+          <t>26130522676300003583</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
@@ -12132,12 +12144,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>342736</t>
+          <t>346658</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>20553</t>
+          <t>88823</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -12147,17 +12159,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>JOEL</t>
+          <t xml:space="preserve">GLORIA </t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>BALTAZAR</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SERVIN</t>
+          <t>LORENZO</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -12167,67 +12179,79 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>6647807329</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>6647556268</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTA FE </t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>23-07-2006</t>
+          <t>05-02-2002</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>6647807329@GMAIL.COM</t>
+          <t>6647556268@GMAIL.COM</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>10-02-2026 17:07:25</t>
+          <t>26-02-2026 09:43:45</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>23-02-2026 16:59:29</t>
+          <t>26-02-2026 09:47:19</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr"/>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>26-02-2026 09:46:49</t>
+        </is>
+      </c>
       <c r="U88" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12235,36 +12259,36 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>26130522589260003351</t>
+          <t>26130522679020003592</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alejandro David  Diaz Quiroga</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>342992</t>
+          <t>345343</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>20809</t>
+          <t>87508</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -12274,17 +12298,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LUIS HECTOR</t>
+          <t>DIEGO GAEL</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>NAVARRETE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ZAMORA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -12294,14 +12318,10 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>6631084871</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>SANTA FE</t>
-        </is>
-      </c>
+          <t>6631996723</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -12309,60 +12329,56 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>01-10-2004</t>
+          <t>11-03-2012</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>6645974918@GMAIL.COM</t>
+          <t>DIEGOGAELNAVARRETE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>11-02-2026 14:45:11</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
+          <t>20-02-2026 16:47:40</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>11-02-2026 14:51:11</t>
+          <t>26-02-2026 18:11:50</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>11-02-2026 14:50:14</t>
-        </is>
-      </c>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12370,14 +12386,22 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>26130522265570002638</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
+          <t>26130522692170003631</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>LILIANA  RAMIREZ  CAMPUZANO</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
@@ -12394,12 +12418,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>346635</t>
+          <t>343679</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>88800</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -12409,17 +12433,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>JHON FREDY</t>
+          <t xml:space="preserve">FELIPE DE JESUS </t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t xml:space="preserve">NARANJO </t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CASTAÑEDA</t>
+          <t>BOJORQUEZ</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -12429,14 +12453,10 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>9902932445</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>STA FE</t>
-        </is>
-      </c>
+          <t>6643056800</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -12444,64 +12464,56 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>15-12-1991</t>
+          <t>21-11-2005</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>JOHNFREDYMADRID@GMAIL.COM</t>
+          <t>6643056800@GMAIL.COM</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>26-02-2026 06:38:48</t>
+          <t>14-02-2026 09:51:20</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>26-02-2026 06:53:14</t>
+          <t>14-02-2026 09:52:12</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>26-02-2026 06:47:24</t>
-        </is>
-      </c>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12509,14 +12521,14 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>26130522676300003583</t>
+          <t>26130522345150002832</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="inlineStr"/>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
@@ -12533,12 +12545,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>346658</t>
+          <t>342736</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>88823</t>
+          <t>20553</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -12548,17 +12560,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLORIA </t>
+          <t>JOEL</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>BALTAZAR</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>LORENZO</t>
+          <t>SERVIN</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -12568,79 +12580,67 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>6647556268</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTA FE </t>
-        </is>
-      </c>
+          <t>6647807329</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>05-02-2002</t>
+          <t>23-07-2006</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>6647556268@GMAIL.COM</t>
+          <t>6647807329@GMAIL.COM</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>26-02-2026 09:43:45</t>
+          <t>10-02-2026 17:07:25</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>26-02-2026 09:47:19</t>
+          <t>23-02-2026 16:59:29</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>26-02-2026 09:46:49</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -12648,24 +12648,24 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>26130522679020003592</t>
+          <t>26130522589260003351</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr"/>
       <c r="Z91" t="inlineStr"/>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>Alejandro David  Diaz Quiroga</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -13625,12 +13625,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>344943</t>
+          <t>345582</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>22760</t>
+          <t>87747</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -13640,17 +13640,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>OMAR</t>
+          <t>DULCE MARIA</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>MENDIVIL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>MENDIVIL</t>
+          <t>BOJORQUEZ</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -13660,79 +13660,67 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>6641231008</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>SANTA FE</t>
-        </is>
-      </c>
+          <t>6643684126</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>12-07-1977</t>
+          <t>26-12-1978</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>6641231008@GMAIL.COM</t>
+          <t>MENDILDULCE78@GMAIL.COM</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>18-02-2026 19:15:58</t>
+          <t>22-02-2026 10:44:34</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>18-02-2026 19:20:34</t>
+          <t>22-02-2026 10:48:11</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>18-02-2026 19:19:54</t>
-        </is>
-      </c>
+          <t>22-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -13740,14 +13728,14 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>26130522474840003120</t>
+          <t>26130522561610003280</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr"/>
       <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
@@ -13764,12 +13752,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>344960</t>
+          <t>344943</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>22777</t>
+          <t>22760</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -13779,27 +13767,27 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>RAFAEL</t>
+          <t>OMAR</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JIMENEZ </t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CHAVARRIA</t>
+          <t>MENDIVIL</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>6196064115</t>
+          <t>6641231008</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -13814,17 +13802,17 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>21-12-1985</t>
+          <t>12-07-1977</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>RJ2434882@GMAIL.COM</t>
+          <t>6641231008@GMAIL.COM</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>18-02-2026 20:27:03</t>
+          <t>18-02-2026 19:15:58</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -13849,7 +13837,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>18-02-2026 20:34:07</t>
+          <t>18-02-2026 19:20:34</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -13859,7 +13847,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>18-02-2026 20:32:43</t>
+          <t>18-02-2026 19:19:54</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -13869,7 +13857,7 @@
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
@@ -13879,7 +13867,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>26130522476810003135</t>
+          <t>26130522474840003120</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr"/>
@@ -13891,24 +13879,24 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Enrique  Silva Reyna</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>345582</t>
+          <t>344960</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>87747</t>
+          <t>22777</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -13918,87 +13906,99 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>DULCE MARIA</t>
+          <t>RAFAEL</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MENDIVIL</t>
+          <t xml:space="preserve"> JIMENEZ </t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>BOJORQUEZ</t>
+          <t>CHAVARRIA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>6643684126</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>6196064115</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>26-12-1978</t>
+          <t>21-12-1985</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>MENDILDULCE78@GMAIL.COM</t>
+          <t>RJ2434882@GMAIL.COM</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>22-02-2026 10:44:34</t>
+          <t>18-02-2026 20:27:03</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>22-02-2026 10:48:11</t>
+          <t>18-02-2026 20:34:07</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>22-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T101" t="inlineStr"/>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>18-02-2026 20:32:43</t>
+        </is>
+      </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V101" t="inlineStr"/>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W101" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -14006,36 +14006,36 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>26130522561610003280</t>
+          <t>26130522476810003135</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="inlineStr"/>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>Luis Enrique  Silva Reyna</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>345889</t>
+          <t>345583</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>88054</t>
+          <t>87748</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -14045,17 +14045,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>EDGARDO HIRAM</t>
+          <t xml:space="preserve">MAXIMILIANO </t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IBAÑEZ </t>
+          <t>PULIDO</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>VILLALOBOS</t>
+          <t xml:space="preserve"> MENDIVIL</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -14065,14 +14065,10 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>6642183103</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>SANTA FE</t>
-        </is>
-      </c>
+          <t>6647602432</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -14080,64 +14076,56 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>30-08-1997</t>
+          <t>27-01-2012</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>IBZEDGAROVILLALOBOS@GMAIL.COM</t>
+          <t>MAXIMCLOUD10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>23-02-2026 16:45:22</t>
+          <t>22-02-2026 10:47:25</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>23-02-2026 16:50:55</t>
+          <t>25-02-2026 19:06:48</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T102" t="inlineStr">
-        <is>
-          <t>23-02-2026 16:50:03</t>
-        </is>
-      </c>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -14145,19 +14133,27 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>26130522588720003349</t>
-        </is>
-      </c>
-      <c r="Y102" t="inlineStr"/>
-      <c r="Z102" t="inlineStr"/>
+          <t>26130522665220003557</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>LILIANA  RAMIREZ  CAMPUZANO</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>Alejandro David  Diaz Quiroga</t>
+          <t>Luis Enrique  Silva Reyna</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -14169,12 +14165,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>345952</t>
+          <t>344951</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>88117</t>
+          <t>22768</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -14184,99 +14180,99 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA </t>
+          <t>JIMMY TAMUJIN</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALANIS </t>
+          <t>GOVEA</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRENES </t>
+          <t>AVILEZ</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>6641374584</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>31-10-1985</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>JYMMYGOVEA973@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>18-02-2026 19:42:55</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>18-02-2026 19:49:29</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>18-02-2026 19:48:36</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>6195599399</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>SANTA FE</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>29-10-1987</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>DIANASOLANO05@ICLOUD.COM</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>23-02-2026 17:59:01</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>Forzoso</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>PROMO FEBRERO 12 MESES</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>25-02-2026 20:10:37</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T103" t="inlineStr">
-        <is>
-          <t>25-02-2026 20:09:00</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="W103" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -14284,19 +14280,11 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>26130522667500003563</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>Yessica Angulo Barragan</t>
-        </is>
-      </c>
+          <t>26130522475710003125</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr"/>
+      <c r="Z103" t="inlineStr"/>
       <c r="AA103" t="inlineStr">
         <is>
           <t>499</t>
@@ -14316,12 +14304,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>344951</t>
+          <t>346656</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>22768</t>
+          <t>88821</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -14331,17 +14319,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>JIMMY TAMUJIN</t>
+          <t xml:space="preserve">OMAR FLORENTINO </t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>GOVEA</t>
+          <t xml:space="preserve">DE AQUINO </t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>AVILEZ</t>
+          <t xml:space="preserve">GALLARDO </t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -14351,7 +14339,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>6641374584</t>
+          <t>6531083309</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -14366,17 +14354,17 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>31-10-1985</t>
+          <t>26-07-2000</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>JYMMYGOVEA973@GMAIL.COM</t>
+          <t>6531083309@GMAIL.COM</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>18-02-2026 19:42:55</t>
+          <t>26-02-2026 09:33:20</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -14401,17 +14389,17 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>18-02-2026 19:49:29</t>
+          <t>26-02-2026 09:42:09</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>26-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>18-02-2026 19:48:36</t>
+          <t>26-02-2026 09:41:36</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -14431,7 +14419,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>26130522475710003125</t>
+          <t>26130522678930003590</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr"/>
@@ -14443,24 +14431,24 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Enrique  Silva Reyna</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>345583</t>
+          <t>345889</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>87748</t>
+          <t>88054</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -14470,17 +14458,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAXIMILIANO </t>
+          <t>EDGARDO HIRAM</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>PULIDO</t>
+          <t xml:space="preserve"> IBAÑEZ </t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MENDIVIL</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -14490,10 +14478,14 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>6647602432</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>6642183103</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -14501,56 +14493,64 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>27-01-2012</t>
+          <t>30-08-1997</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>MAXIMCLOUD10@GMAIL.COM</t>
+          <t>IBZEDGAROVILLALOBOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>22-02-2026 10:47:25</t>
+          <t>23-02-2026 16:45:22</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>25-02-2026 19:06:48</t>
+          <t>23-02-2026 16:50:55</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T105" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>23-02-2026 16:50:03</t>
+        </is>
+      </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V105" t="inlineStr"/>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W105" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -14558,27 +14558,19 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>26130522665220003557</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>LILIANA  RAMIREZ  CAMPUZANO</t>
-        </is>
-      </c>
+          <t>26130522588720003349</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr"/>
+      <c r="Z105" t="inlineStr"/>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>Luis Enrique  Silva Reyna</t>
+          <t>Alejandro David  Diaz Quiroga</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -14590,12 +14582,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>346214</t>
+          <t>345952</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>88379</t>
+          <t>88117</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -14605,30 +14597,34 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>GRICELDA</t>
+          <t xml:space="preserve">DIANA </t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> DIAZ</t>
+          <t xml:space="preserve">ALANIS </t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MEDINA</t>
+          <t xml:space="preserve">BRENES </t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>6644335878</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>6195599399</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -14636,56 +14632,64 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>05-12-1988</t>
+          <t>29-10-1987</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>GRICELDADIAZ323@GMAIL.COM</t>
+          <t>DIANASOLANO05@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>24-02-2026 16:32:01</t>
+          <t>23-02-2026 17:59:01</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>24-02-2026 16:33:39</t>
+          <t>25-02-2026 20:10:37</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T106" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>25-02-2026 20:09:00</t>
+        </is>
+      </c>
       <c r="U106" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V106" t="inlineStr"/>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W106" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -14693,36 +14697,44 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>26130522624860003448</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr"/>
-      <c r="Z106" t="inlineStr"/>
+          <t>26130522667500003563</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>Yessica Angulo Barragan</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>Jose Alfredo Andraca Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>344945</t>
+          <t>346032</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>22762</t>
+          <t>88197</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -14732,17 +14744,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>MARY CARMMEN</t>
+          <t xml:space="preserve">OMAR </t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GARCIA</t>
+          <t xml:space="preserve">LARA </t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MARMOLEJO</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -14752,7 +14764,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>6641884300</t>
+          <t>6645840074</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -14762,22 +14774,22 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>23-03-1984</t>
+          <t>21-11-2012</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>MARYCGM84@GMAIL.COM</t>
+          <t>6645840074@GMAIL.COM</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>18-02-2026 19:17:16</t>
+          <t>23-02-2026 19:39:47</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -14802,17 +14814,17 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>18-02-2026 19:28:37</t>
+          <t>23-02-2026 19:45:43</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>18-02-2026 19:24:38</t>
+          <t>23-02-2026 19:45:09</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -14832,7 +14844,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>26130522475120003122</t>
+          <t>26130522600430003394</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr"/>
@@ -14856,12 +14868,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>346656</t>
+          <t>346050</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>88821</t>
+          <t>88215</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -14871,17 +14883,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">OMAR FLORENTINO </t>
+          <t>JHOSELIN ARLETTE</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE AQUINO </t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALLARDO </t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -14891,7 +14903,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>6531083309</t>
+          <t>6646329256</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -14901,22 +14913,22 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>26-07-2000</t>
+          <t>09-12-2001</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>6531083309@GMAIL.COM</t>
+          <t>ARLETTEJB1712@GMAIL.COM</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>26-02-2026 09:33:20</t>
+          <t>23-02-2026 20:45:52</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -14941,17 +14953,17 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>26-02-2026 09:42:09</t>
+          <t>23-02-2026 20:49:50</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>26-02-2026 09:41:36</t>
+          <t>23-02-2026 20:49:16</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -14961,7 +14973,7 @@
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
@@ -14971,7 +14983,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>26130522678930003590</t>
+          <t>26130522602110003404</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr"/>
@@ -14983,24 +14995,24 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>Luis Enrique  Silva Reyna</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>345014</t>
+          <t>344945</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>22831</t>
+          <t>22762</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -15010,17 +15022,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ANAMAR</t>
+          <t>MARY CARMMEN</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORENO </t>
+          <t xml:space="preserve"> GARCIA</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t xml:space="preserve"> MARMOLEJO</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -15030,10 +15042,14 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>6642183298</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>6641884300</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -15041,56 +15057,64 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>30-08-1996</t>
+          <t>23-03-1984</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>ANIZZGUZMAN_@HOTMAIL.COM</t>
+          <t>MARYCGM84@GMAIL.COM</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>19-02-2026 09:32:14</t>
+          <t>18-02-2026 19:17:16</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>19-02-2026 09:36:23</t>
+          <t>18-02-2026 19:28:37</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>19-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T109" t="inlineStr"/>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>18-02-2026 19:24:38</t>
+        </is>
+      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V109" t="inlineStr"/>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W109" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -15098,36 +15122,36 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>26130522490280003150</t>
+          <t>26130522475120003122</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr"/>
       <c r="Z109" t="inlineStr"/>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Luis Enrique  Silva Reyna</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>346051</t>
+          <t>346214</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>88216</t>
+          <t>88379</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -15137,17 +15161,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>BRYAN IRAN</t>
+          <t>GRICELDA</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> JAUREGUI</t>
+          <t xml:space="preserve"> DIAZ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> BELTRAN</t>
+          <t xml:space="preserve"> MEDINA</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -15157,79 +15181,67 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>6631667265</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>SANTA FE</t>
-        </is>
-      </c>
+          <t>6644335878</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>25-10-2005</t>
+          <t>05-12-1988</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>JAUREGUIB2510@GMAIL.COM</t>
+          <t>GRICELDADIAZ323@GMAIL.COM</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>23-02-2026 20:46:45</t>
+          <t>24-02-2026 16:32:01</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>23-02-2026 20:53:01</t>
+          <t>24-02-2026 16:33:39</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>23-02-2026 20:52:04</t>
-        </is>
-      </c>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -15237,36 +15249,36 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>26130522602170003405</t>
+          <t>26130522624860003448</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr"/>
       <c r="Z110" t="inlineStr"/>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Alfredo Andraca Rodriguez</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>346032</t>
+          <t>346051</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>88197</t>
+          <t>88216</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -15276,17 +15288,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">OMAR </t>
+          <t>BRYAN IRAN</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">LARA </t>
+          <t xml:space="preserve"> JAUREGUI</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve"> BELTRAN</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -15296,7 +15308,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>6645840074</t>
+          <t>6631667265</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -15311,17 +15323,17 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>21-11-2012</t>
+          <t>25-10-2005</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>6645840074@GMAIL.COM</t>
+          <t>JAUREGUIB2510@GMAIL.COM</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>23-02-2026 19:39:47</t>
+          <t>23-02-2026 20:46:45</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -15346,7 +15358,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>23-02-2026 19:45:43</t>
+          <t>23-02-2026 20:53:01</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -15356,7 +15368,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>23-02-2026 19:45:09</t>
+          <t>23-02-2026 20:52:04</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -15376,7 +15388,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>26130522600430003394</t>
+          <t>26130522602170003405</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr"/>
@@ -15388,24 +15400,24 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>Luis Enrique  Silva Reyna</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>346050</t>
+          <t>346263</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>88215</t>
+          <t>88428</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -15415,17 +15427,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>JHOSELIN ARLETTE</t>
+          <t>DULCE GUADALUPE</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>DE JESUS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>DE JESUS</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -15435,12 +15447,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>6646329256</t>
+          <t>6631103366</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>STA FE</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -15450,17 +15462,17 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>09-12-2001</t>
+          <t>18-12-2004</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>ARLETTEJB1712@GMAIL.COM</t>
+          <t>6632239717@GMAIL.COM</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>23-02-2026 20:45:52</t>
+          <t>24-02-2026 17:37:39</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -15485,17 +15497,17 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>23-02-2026 20:49:50</t>
+          <t>26-02-2026 05:15:51</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>26-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>23-02-2026 20:49:16</t>
+          <t>26-02-2026 05:15:10</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -15505,7 +15517,7 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
@@ -15515,11 +15527,19 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>26130522602110003404</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr"/>
-      <c r="Z112" t="inlineStr"/>
+          <t>26130522670110003575</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>MARIA CANDELARIA LARA AVILA</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>499</t>
@@ -15539,12 +15559,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>345954</t>
+          <t>346334</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>88119</t>
+          <t>88499</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -15554,17 +15574,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ALEXA JOANA</t>
+          <t>ITZIA YUNUEM</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>SOLANO</t>
+          <t xml:space="preserve"> GAXIOLA</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ALANIS</t>
+          <t xml:space="preserve"> AVALOS</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -15574,12 +15594,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>6641100795</t>
+          <t>6631274690</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SN FRANCESCO</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -15589,17 +15609,17 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>01-05-2005</t>
+          <t>23-09-1992</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>6641100795@GMAIL.COM</t>
+          <t>ITZIAGAX@YAHOO.COM</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>23-02-2026 17:59:18</t>
+          <t>24-02-2026 20:45:26</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -15624,7 +15644,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>24-02-2026 10:46:41</t>
+          <t>24-02-2026 20:53:36</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -15634,7 +15654,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>24-02-2026 10:45:33</t>
+          <t>24-02-2026 20:52:22</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -15644,7 +15664,7 @@
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
@@ -15654,19 +15674,11 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>26130522615880003427</t>
-        </is>
-      </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>MARIA CANDELARIA LARA AVILA</t>
-        </is>
-      </c>
+          <t>26130522637480003489</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr"/>
+      <c r="Z113" t="inlineStr"/>
       <c r="AA113" t="inlineStr">
         <is>
           <t>499</t>
@@ -15686,12 +15698,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>346002</t>
+          <t>346699</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>88167</t>
+          <t>88864</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -15701,17 +15713,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>REBECA</t>
+          <t>ERASMO CARLOS</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ARREDONDO CEPEDA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>PENNOCK</t>
+          <t>ZAMARRON</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -15721,28 +15733,28 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>6644710954</t>
+          <t>3113733607</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>28-04-2004</t>
+          <t>02-12-1986</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>REBEACP@GMAIL.COM</t>
+          <t>ERASMOCARLOSTORRESZAMARRON@GMAIL.COM</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>23-02-2026 18:46:41</t>
+          <t>26-02-2026 13:05:09</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -15767,12 +15779,12 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>23-02-2026 18:48:19</t>
+          <t>26-02-2026 13:06:47</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>26-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T114" t="inlineStr"/>
@@ -15789,7 +15801,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>26130522597230003378</t>
+          <t>26130522682130003600</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr"/>
@@ -15813,12 +15825,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>346715</t>
+          <t>345014</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>88880</t>
+          <t>22831</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -15828,17 +15840,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>FERNANDA</t>
+          <t>ANAMAR</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>VALERIO</t>
+          <t xml:space="preserve">MORENO </t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -15848,7 +15860,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>6647828225</t>
+          <t>6642183298</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -15859,17 +15871,17 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>02-06-2002</t>
+          <t>30-08-1996</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>6647828225@GMAIL.COM</t>
+          <t>ANIZZGUZMAN_@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>26-02-2026 14:34:57</t>
+          <t>19-02-2026 09:32:14</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -15884,28 +15896,28 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>26-02-2026 14:35:50</t>
+          <t>19-02-2026 09:36:23</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
+          <t>19-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V115" t="inlineStr"/>
@@ -15916,14 +15928,14 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>26130522683610003605</t>
+          <t>26130522490280003150</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr"/>
       <c r="Z115" t="inlineStr"/>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
@@ -15940,12 +15952,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>346822</t>
+          <t>346715</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>88987</t>
+          <t>88880</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -15955,17 +15967,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>JUAN MANUEL</t>
+          <t>FERNANDA</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>VALERIO</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SOTO</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -15975,33 +15987,33 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>6634449912</t>
+          <t>6647828225</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>11-10-2010</t>
+          <t>02-06-2002</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>6634449912@GMAIL.COM</t>
+          <t>6647828225@GMAIL.COM</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>26-02-2026 19:13:04</t>
+          <t>26-02-2026 14:34:57</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -16011,17 +16023,17 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>26-02-2026 19:14:29</t>
+          <t>26-02-2026 14:35:50</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -16032,7 +16044,7 @@
       <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V116" t="inlineStr"/>
@@ -16043,14 +16055,14 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>26130522694950003639</t>
+          <t>26130522683610003605</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr"/>
       <c r="Z116" t="inlineStr"/>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
@@ -16067,12 +16079,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>346263</t>
+          <t>346822</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>88428</t>
+          <t>88987</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -16082,17 +16094,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>DULCE GUADALUPE</t>
+          <t>JUAN MANUEL</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>DE JESUS</t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>DE JESUS</t>
+          <t xml:space="preserve"> SOTO</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -16102,57 +16114,53 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>6631103366</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>STA FE</t>
-        </is>
-      </c>
+          <t>6634449912</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>18-12-2004</t>
+          <t>11-10-2010</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>6632239717@GMAIL.COM</t>
+          <t>6634449912@GMAIL.COM</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>24-02-2026 17:37:39</t>
+          <t>26-02-2026 19:13:04</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>26-02-2026 05:15:51</t>
+          <t>26-02-2026 19:14:29</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -16160,21 +16168,13 @@
           <t>26-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>26-02-2026 05:15:10</t>
-        </is>
-      </c>
+      <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V117" t="inlineStr"/>
       <c r="W117" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -16182,22 +16182,14 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>26130522670110003575</t>
-        </is>
-      </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>MARIA CANDELARIA LARA AVILA</t>
-        </is>
-      </c>
+          <t>26130522694950003639</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr"/>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
@@ -16214,12 +16206,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>346334</t>
+          <t>345954</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>88499</t>
+          <t>88119</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -16229,17 +16221,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ITZIA YUNUEM</t>
+          <t>ALEXA JOANA</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> GAXIOLA</t>
+          <t>SOLANO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AVALOS</t>
+          <t>ALANIS</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -16249,12 +16241,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>6631274690</t>
+          <t>6641100795</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>SN FRANCESCO</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -16264,17 +16256,17 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>23-09-1992</t>
+          <t>01-05-2005</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>ITZIAGAX@YAHOO.COM</t>
+          <t>6641100795@GMAIL.COM</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>24-02-2026 20:45:26</t>
+          <t>23-02-2026 17:59:18</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -16299,7 +16291,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>24-02-2026 20:53:36</t>
+          <t>24-02-2026 10:46:41</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -16309,7 +16301,7 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>24-02-2026 20:52:22</t>
+          <t>24-02-2026 10:45:33</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -16319,7 +16311,7 @@
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
@@ -16329,11 +16321,19 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>26130522637480003489</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr"/>
-      <c r="Z118" t="inlineStr"/>
+          <t>26130522615880003427</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>MARIA CANDELARIA LARA AVILA</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>499</t>
@@ -16353,12 +16353,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>346699</t>
+          <t>346002</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>88864</t>
+          <t>88167</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -16368,17 +16368,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ERASMO CARLOS</t>
+          <t>REBECA</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t xml:space="preserve"> ARREDONDO CEPEDA</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ZAMARRON</t>
+          <t>PENNOCK</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -16388,28 +16388,28 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>3113733607</t>
+          <t>6644710954</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>02-12-1986</t>
+          <t>28-04-2004</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>ERASMOCARLOSTORRESZAMARRON@GMAIL.COM</t>
+          <t>REBEACP@GMAIL.COM</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>26-02-2026 13:05:09</t>
+          <t>23-02-2026 18:46:41</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -16434,12 +16434,12 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>26-02-2026 13:06:47</t>
+          <t>23-02-2026 18:48:19</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T119" t="inlineStr"/>
@@ -16456,7 +16456,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>26130522682130003600</t>
+          <t>26130522597230003378</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr"/>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SANTA FE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SANTA FE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347581</t>
+          <t>346084</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89746</t>
+          <t>88249</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IKER DAVID</t>
+          <t>ADILENE LIZETH</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t xml:space="preserve">GUZMAN </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">MARINO </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,43 +740,47 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6643423254</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6642307004</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>STA FE</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>28-01-2010</t>
+          <t>16-06-1998</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6643423254@GMAIL.COM</t>
+          <t>6642307004@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 14:06:11</t>
+          <t>24-02-2026 08:12:15</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -786,7 +790,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 14:06:56</t>
+          <t>02-03-2026 07:28:13</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -794,13 +798,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>02-03-2026 07:27:14</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -808,11 +820,19 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26130522794110003813</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+          <t>26130522782370003772</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Yessica Angulo Barragan</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>549</t>
@@ -820,24 +840,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Alejandro David  Diaz Quiroga</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>346084</t>
+          <t>347167</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>88249</t>
+          <t>89332</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ADILENE LIZETH</t>
+          <t>AYLIN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUZMAN </t>
+          <t>CAMPOY</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARINO </t>
+          <t>DURAN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -867,12 +887,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6642307004</t>
+          <t>6161236916</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>STA FE</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -882,17 +902,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>16-06-1998</t>
+          <t>19-09-2003</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6642307004@GMAIL.COM</t>
+          <t>6161236916@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>24-02-2026 08:12:15</t>
+          <t>28-02-2026 09:43:47</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -902,32 +922,32 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 07:28:13</t>
+          <t>01-03-2026 13:51:19</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>02-03-2026 07:27:14</t>
+          <t>01-03-2026 13:50:09</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -947,7 +967,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26130522782370003772</t>
+          <t>26130522770130003755</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -962,7 +982,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -979,12 +999,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347167</t>
+          <t>347393</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89332</t>
+          <t>89558</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -994,17 +1014,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AYLIN</t>
+          <t xml:space="preserve">EMMANUEL EDAIN </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CAMPOY</t>
+          <t>RENTERIA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DURAN</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,67 +1034,67 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6161236916</t>
+          <t>6647534980</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>STA FE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>19-09-2003</t>
+          <t>30-04-2007</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>6161236916@GMAIL.COM</t>
+          <t>RENTERIASANCHEZEMMANUEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>28-02-2026 09:43:47</t>
+          <t>02-03-2026 05:52:47</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>01-03-2026 13:51:19</t>
+          <t>03-03-2026 06:05:34</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>01-03-2026 13:50:09</t>
+          <t>03-03-2026 06:04:45</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1094,7 +1114,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26130522770130003755</t>
+          <t>26130522824140003888</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1104,12 +1124,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Yessica Angulo Barragan</t>
+          <t>ERIKA  RUIZ GONZALEZ</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1126,12 +1146,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347579</t>
+          <t>347581</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89744</t>
+          <t>89746</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1141,19 +1161,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ARMANDO DAVID</t>
+          <t>IKER DAVID</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>DAVILA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>RODRIGUEZ</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>HERMOSILLO</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>52</t>
@@ -1161,7 +1181,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6633284436</t>
+          <t>6643423254</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,17 +1192,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>07-09-2010</t>
+          <t>28-01-2010</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>6633284436@GMAIL.COM</t>
+          <t>6643423254@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 13:57:53</t>
+          <t>02-03-2026 14:06:11</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1207,7 +1227,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 13:58:56</t>
+          <t>02-03-2026 14:06:56</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1229,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26130522793900003812</t>
+          <t>26130522794110003813</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1253,12 +1273,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347578</t>
+          <t>347579</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89743</t>
+          <t>89744</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1268,17 +1288,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ISSAC RICARDO</t>
+          <t>ARMANDO DAVID</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>HERMOSILLO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1288,7 +1308,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6648285903</t>
+          <t>6633284436</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1299,17 +1319,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>30-03-2010</t>
+          <t>07-09-2010</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ISSACRICARDOGARCIA@GMAIL.COM</t>
+          <t>6633284436@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 13:54:20</t>
+          <t>02-03-2026 13:57:53</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1334,7 +1354,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 13:56:23</t>
+          <t>02-03-2026 13:58:56</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1356,7 +1376,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26130522793860003811</t>
+          <t>26130522793900003812</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1380,12 +1400,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347701</t>
+          <t>347578</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89866</t>
+          <t>89743</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1395,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATILDE </t>
+          <t>ISSAC RICARDO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELAZQUEZ </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1415,28 +1435,28 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6647329461</t>
+          <t>6648285903</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>14-03-1963</t>
+          <t>30-03-2010</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6647329461@GMAIL.COM</t>
+          <t>ISSACRICARDOGARCIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:06</t>
+          <t>02-03-2026 13:54:20</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1461,7 +1481,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 16:47:21</t>
+          <t>02-03-2026 13:56:23</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1472,7 +1492,7 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1483,7 +1503,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26130522803110003831</t>
+          <t>26130522793860003811</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1495,10 +1515,657 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>Alejandro David  Diaz Quiroga</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>347979</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>90144</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA ELENA </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BARRAGAN </t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROMERO </t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3279785050</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTA FE </t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>31-05-1972</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3279785050@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:56:39</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:04:01</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:03:20</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>26130522834330003904</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Jose Alfredo Andraca Rodriguez</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>347701</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>89866</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MATILDE </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOPEZ </t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VELAZQUEZ </t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6647329461</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>14-03-1963</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6647329461@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:46:06</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:47:21</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26130522803110003831</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>347983</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>90148</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CHRISTIAN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BENITEZ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6644451633</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>22-07-2006</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>CHISTIANGB563@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:06:09</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:10:12</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26130522834480003906</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>347950</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>90115</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>OMAR ISAID</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6648172166</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>15-04-2004</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>OISF16483@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>03-03-2026 07:29:11</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>03-03-2026 07:31:02</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26130522831810003893</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Jose Alfredo Andraca Rodriguez</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>348124</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>90289</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MAR</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PAZ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6641690818</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>03-09-1997</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>JUAN.MAR@UABC.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:35:17</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:36:19</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26130522847190003941</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SANTA FE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SANTA FE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347453</t>
+          <t>346084</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89618</t>
+          <t>88249</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PERLA NARITALY</t>
+          <t>ADILENE LIZETH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t xml:space="preserve">GUZMAN </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t xml:space="preserve">MARINO </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,10 +613,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6643090938</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>6642307004</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>STA FE</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -624,32 +628,32 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30-12-1991</t>
+          <t>16-06-1998</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>PENANUOS@GMAIL.COM</t>
+          <t>6642307004@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-03-2026 08:46:02</t>
+          <t>24-02-2026 08:12:15</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -659,7 +663,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 08:47:32</t>
+          <t>02-03-2026 07:28:13</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -667,13 +671,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>02-03-2026 07:27:14</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -681,11 +693,19 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26130522784650003780</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>26130522782370003772</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Yessica Angulo Barragan</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>549</t>
@@ -693,24 +713,24 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Irving Correa Franco</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>346084</t>
+          <t>347167</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>88249</t>
+          <t>89332</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +740,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ADILENE LIZETH</t>
+          <t>AYLIN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUZMAN </t>
+          <t>CAMPOY</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARINO </t>
+          <t>DURAN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,12 +760,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6642307004</t>
+          <t>6161236916</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>STA FE</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -755,17 +775,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16-06-1998</t>
+          <t>19-09-2003</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6642307004@GMAIL.COM</t>
+          <t>6161236916@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>24-02-2026 08:12:15</t>
+          <t>28-02-2026 09:43:47</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -775,32 +795,32 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 07:28:13</t>
+          <t>01-03-2026 13:51:19</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>02-03-2026 07:27:14</t>
+          <t>01-03-2026 13:50:09</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -820,7 +840,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26130522782370003772</t>
+          <t>26130522770130003755</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -835,7 +855,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -852,12 +872,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347167</t>
+          <t>347393</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89332</t>
+          <t>89558</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +887,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AYLIN</t>
+          <t xml:space="preserve">EMMANUEL EDAIN </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CAMPOY</t>
+          <t>RENTERIA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DURAN</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,67 +907,67 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6161236916</t>
+          <t>6647534980</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>STA FE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>19-09-2003</t>
+          <t>30-04-2007</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>6161236916@GMAIL.COM</t>
+          <t>RENTERIASANCHEZEMMANUEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>28-02-2026 09:43:47</t>
+          <t>02-03-2026 05:52:47</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>01-03-2026 13:51:19</t>
+          <t>03-03-2026 06:05:34</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>01-03-2026 13:50:09</t>
+          <t>03-03-2026 06:04:45</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -967,7 +987,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26130522770130003755</t>
+          <t>26130522824140003888</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -977,12 +997,12 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Yessica Angulo Barragan</t>
+          <t>ERIKA  RUIZ GONZALEZ</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -999,12 +1019,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347393</t>
+          <t>347578</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89558</t>
+          <t>89743</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1014,17 +1034,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMMANUEL EDAIN </t>
+          <t>ISSAC RICARDO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RENTERIA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1034,14 +1054,10 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6647534980</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>STA FE</t>
-        </is>
-      </c>
+          <t>6648285903</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1049,32 +1065,32 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>30-04-2007</t>
+          <t>30-03-2010</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>RENTERIASANCHEZEMMANUEL@GMAIL.COM</t>
+          <t>ISSACRICARDOGARCIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 05:52:47</t>
+          <t>02-03-2026 13:54:20</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1084,29 +1100,21 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-03-2026 06:05:34</t>
+          <t>02-03-2026 13:56:23</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>03-03-2026 06:04:45</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1114,19 +1122,11 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26130522824140003888</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>ERIKA  RUIZ GONZALEZ</t>
-        </is>
-      </c>
+          <t>26130522793860003811</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
           <t>549</t>
@@ -1134,24 +1134,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alejandro David  Diaz Quiroga</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347581</t>
+          <t>347979</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89746</t>
+          <t>90144</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IKER DAVID</t>
+          <t xml:space="preserve">MARIA ELENA </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t xml:space="preserve">BARRAGAN </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">ROMERO </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1181,67 +1181,79 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6643423254</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>3279785050</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTA FE </t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>28-01-2010</t>
+          <t>31-05-1972</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>6643423254@GMAIL.COM</t>
+          <t>3279785050@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 14:06:11</t>
+          <t>03-03-2026 08:56:39</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 14:06:56</t>
+          <t>03-03-2026 09:04:01</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:03:20</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1249,19 +1261,19 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26130522794110003813</t>
+          <t>26130522834330003904</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Alejandro David  Diaz Quiroga</t>
+          <t>Jose Alfredo Andraca Rodriguez</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1400,12 +1412,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347578</t>
+          <t>347453</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89743</t>
+          <t>89618</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1427,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ISSAC RICARDO</t>
+          <t>PERLA NARITALY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,28 +1447,28 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6648285903</t>
+          <t>6643090938</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>30-03-2010</t>
+          <t>30-12-1991</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ISSACRICARDOGARCIA@GMAIL.COM</t>
+          <t>PENANUOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 13:54:20</t>
+          <t>02-03-2026 08:46:02</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1481,7 +1493,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 13:56:23</t>
+          <t>02-03-2026 08:47:32</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1492,7 +1504,7 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1503,7 +1515,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26130522793860003811</t>
+          <t>26130522784650003780</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1515,7 +1527,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Alejandro David  Diaz Quiroga</t>
+          <t>Irving Correa Franco</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1527,12 +1539,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347979</t>
+          <t>347581</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90144</t>
+          <t>89746</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1542,17 +1554,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA ELENA </t>
+          <t>IKER DAVID</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARRAGAN </t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROMERO </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1562,79 +1574,67 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3279785050</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SANTA FE </t>
-        </is>
-      </c>
+          <t>6643423254</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>31-05-1972</t>
+          <t>28-01-2010</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3279785050@GMAIL.COM</t>
+          <t>6643423254@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>03-03-2026 08:56:39</t>
+          <t>02-03-2026 14:06:11</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-03-2026 09:04:01</t>
+          <t>02-03-2026 14:06:56</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>03-03-2026 09:03:20</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1642,19 +1642,19 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26130522834330003904</t>
+          <t>26130522794110003813</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Jose Alfredo Andraca Rodriguez</t>
+          <t>Alejandro David  Diaz Quiroga</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1920,12 +1920,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347950</t>
+          <t>348796</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90115</t>
+          <t>90961</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1935,17 +1935,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OMAR ISAID</t>
+          <t xml:space="preserve">GAEL ALEJANDRO </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>TOPETE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t xml:space="preserve"> PANTOJA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6648172166</t>
+          <t>6653472345</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1966,22 +1966,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>15-04-2004</t>
+          <t>07-11-2006</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>OISF16483@GMAIL.COM</t>
+          <t>CERIAL4367@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-03-2026 07:29:11</t>
+          <t>05-03-2026 18:49:34</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1991,28 +1991,28 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 07:31:02</t>
+          <t>05-03-2026 18:51:30</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -2023,36 +2023,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26130522831810003893</t>
+          <t>26130522928290004140</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Jose Alfredo Andraca Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>348124</t>
+          <t>347950</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90289</t>
+          <t>90115</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,17 +2062,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t>OMAR ISAID</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MAR</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PAZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6641690818</t>
+          <t>6648172166</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2093,17 +2093,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>03-09-1997</t>
+          <t>15-04-2004</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>JUAN.MAR@UABC.EDU.MX</t>
+          <t>OISF16483@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-03-2026 16:35:17</t>
+          <t>03-03-2026 07:29:11</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-03-2026 16:36:19</t>
+          <t>03-03-2026 07:31:02</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26130522847190003941</t>
+          <t>26130522831810003893</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2162,10 +2162,526 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
+          <t>Jose Alfredo Andraca Rodriguez</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>348636</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>90801</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>JIMENEZ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>9096424576</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>STA FE</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>11-03-2000</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>PEDRO.J1MENEZ1904@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>05-03-2026 08:52:29</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>05-03-2026 08:57:55</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>05-03-2026 08:56:52</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26130522911120004098</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>348124</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90289</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MAR</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PAZ</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6641690818</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>03-09-1997</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>JUAN.MAR@UABC.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:35:17</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:36:19</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26130522847190003941</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348341</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90506</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PABLO GAEL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6644965147</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>14-07-2010</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>VAZQUEZPEREZ862@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>04-03-2026 07:57:42</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>04-03-2026 07:59:00</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26130522874980004010</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Irving Correa Franco</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>348575</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>90740</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EVA ESTELA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MEDINA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ESPARZA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6641111100</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>27-01-2000</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>EVAESTELAMEDINAESPARZA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:44:13</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>MENSUALIDAD FARMACIAS SIMILARES $399</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:45:01</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26130522895460004065</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SANTA FE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SANTA FE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>346084</t>
+          <t>340230</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88249</t>
+          <t>18048</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ADILENE LIZETH</t>
+          <t>JOSEPH IVAN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUZMAN </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARINO </t>
+          <t>ANDRADE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,37 +613,37 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6642307004</t>
+          <t>6645548774</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>STA FE</t>
+          <t>FSD</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>16-06-1998</t>
+          <t>16-10-1998</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6642307004@GMAIL.COM</t>
+          <t>ALARKANTOS210@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>24-02-2026 08:12:15</t>
+          <t>02-02-2026 15:49:31</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 07:28:13</t>
+          <t>06-03-2026 18:57:07</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>02-03-2026 07:27:14</t>
+          <t>06-03-2026 18:56:41</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26130522782370003772</t>
+          <t>26070522959610004903</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Yessica Angulo Barragan</t>
+          <t>MARIA CANDELARIA LARA AVILA</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -725,12 +725,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347167</t>
+          <t>346084</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89332</t>
+          <t>88249</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -740,17 +740,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AYLIN</t>
+          <t>ADILENE LIZETH</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CAMPOY</t>
+          <t xml:space="preserve">GUZMAN </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DURAN</t>
+          <t xml:space="preserve">MARINO </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6161236916</t>
+          <t>6642307004</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>STA FE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -775,17 +775,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>19-09-2003</t>
+          <t>16-06-1998</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6161236916@GMAIL.COM</t>
+          <t>6642307004@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>28-02-2026 09:43:47</t>
+          <t>24-02-2026 08:12:15</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -795,22 +795,22 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>01-03-2026 13:51:19</t>
+          <t>02-03-2026 07:28:13</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>01-03-2026 13:50:09</t>
+          <t>02-03-2026 07:27:14</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26130522770130003755</t>
+          <t>26130522782370003772</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -872,12 +872,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347393</t>
+          <t>347453</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89558</t>
+          <t>89618</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMMANUEL EDAIN </t>
+          <t>PERLA NARITALY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RENTERIA</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -907,47 +907,43 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6647534980</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>STA FE</t>
-        </is>
-      </c>
+          <t>6643090938</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>30-04-2007</t>
+          <t>30-12-1991</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>RENTERIASANCHEZEMMANUEL@GMAIL.COM</t>
+          <t>PENANUOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 05:52:47</t>
+          <t>02-03-2026 08:46:02</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -957,29 +953,21 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-03-2026 06:05:34</t>
+          <t>02-03-2026 08:47:32</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>03-03-2026 06:04:45</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -987,19 +975,11 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26130522824140003888</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>ERIKA  RUIZ GONZALEZ</t>
-        </is>
-      </c>
+          <t>26130522784650003780</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>549</t>
@@ -1007,24 +987,24 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Irving Correa Franco</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347578</t>
+          <t>347581</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89743</t>
+          <t>89746</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1034,17 +1014,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ISSAC RICARDO</t>
+          <t>IKER DAVID</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1054,7 +1034,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6648285903</t>
+          <t>6643423254</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,17 +1045,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>30-03-2010</t>
+          <t>28-01-2010</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ISSACRICARDOGARCIA@GMAIL.COM</t>
+          <t>6643423254@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 13:54:20</t>
+          <t>02-03-2026 14:06:11</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1100,12 +1080,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 13:56:23</t>
+          <t>02-03-2026 14:06:56</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1122,7 +1102,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26130522793860003811</t>
+          <t>26130522794110003813</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1146,12 +1126,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347979</t>
+          <t>347167</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90144</t>
+          <t>89332</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1161,17 +1141,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA ELENA </t>
+          <t>AYLIN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARRAGAN </t>
+          <t>CAMPOY</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROMERO </t>
+          <t>DURAN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1181,12 +1161,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3279785050</t>
+          <t>6161236916</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTA FE </t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1196,17 +1176,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>31-05-1972</t>
+          <t>19-09-2003</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3279785050@GMAIL.COM</t>
+          <t>6161236916@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>03-03-2026 08:56:39</t>
+          <t>28-02-2026 09:43:47</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1231,17 +1211,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 09:04:01</t>
+          <t>01-03-2026 13:51:19</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>03-03-2026 09:03:20</t>
+          <t>01-03-2026 13:50:09</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1261,11 +1241,19 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26130522834330003904</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26130522770130003755</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Yessica Angulo Barragan</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>649</t>
@@ -1273,12 +1261,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Jose Alfredo Andraca Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1359,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1412,12 +1400,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347453</t>
+          <t>347578</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89618</t>
+          <t>89743</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1427,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PERLA NARITALY</t>
+          <t>ISSAC RICARDO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1447,28 +1435,28 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6643090938</t>
+          <t>6648285903</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>30-12-1991</t>
+          <t>30-03-2010</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PENANUOS@GMAIL.COM</t>
+          <t>ISSACRICARDOGARCIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 08:46:02</t>
+          <t>02-03-2026 13:54:20</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1493,18 +1481,18 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 08:47:32</t>
+          <t>02-03-2026 13:56:23</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1515,7 +1503,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26130522784650003780</t>
+          <t>26130522793860003811</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1527,7 +1515,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Irving Correa Franco</t>
+          <t>Alejandro David  Diaz Quiroga</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1539,12 +1527,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347581</t>
+          <t>347701</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89746</t>
+          <t>89866</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1554,17 +1542,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IKER DAVID</t>
+          <t xml:space="preserve">MATILDE </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">VELAZQUEZ </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1574,28 +1562,28 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6643423254</t>
+          <t>6647329461</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>28-01-2010</t>
+          <t>14-03-1963</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6643423254@GMAIL.COM</t>
+          <t>6647329461@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 14:06:11</t>
+          <t>02-03-2026 16:46:06</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1620,18 +1608,18 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 14:06:56</t>
+          <t>02-03-2026 16:47:21</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1642,7 +1630,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26130522794110003813</t>
+          <t>26130522803110003831</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1654,24 +1642,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Alejandro David  Diaz Quiroga</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347701</t>
+          <t>347983</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89866</t>
+          <t>90148</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1681,17 +1669,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATILDE </t>
+          <t>CHRISTIAN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELAZQUEZ </t>
+          <t>BENITEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1701,28 +1689,28 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6647329461</t>
+          <t>6644451633</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>14-03-1963</t>
+          <t>22-07-2006</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>6647329461@GMAIL.COM</t>
+          <t>CHISTIANGB563@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:06</t>
+          <t>03-03-2026 09:06:09</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1747,7 +1735,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 16:47:21</t>
+          <t>03-03-2026 09:10:12</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1769,7 +1757,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26130522803110003831</t>
+          <t>26130522834480003906</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1793,12 +1781,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347983</t>
+          <t>347950</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90148</t>
+          <t>90115</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1808,17 +1796,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CHRISTIAN</t>
+          <t>OMAR ISAID</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BENITEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1828,7 +1816,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6644451633</t>
+          <t>6648172166</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1839,22 +1827,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>22-07-2006</t>
+          <t>15-04-2004</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CHISTIANGB563@GMAIL.COM</t>
+          <t>OISF16483@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 09:06:09</t>
+          <t>03-03-2026 07:29:11</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1864,28 +1852,28 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 09:10:12</t>
+          <t>03-03-2026 07:31:02</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1896,36 +1884,36 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26130522834480003906</t>
+          <t>26130522831810003893</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Alfredo Andraca Rodriguez</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>348796</t>
+          <t>347393</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90961</t>
+          <t>89558</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1935,17 +1923,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAEL ALEJANDRO </t>
+          <t xml:space="preserve">EMMANUEL EDAIN </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TOPETE</t>
+          <t>RENTERIA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PANTOJA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1955,10 +1943,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6653472345</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6647534980</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>STA FE</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1966,32 +1958,32 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>07-11-2006</t>
+          <t>30-04-2007</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CERIAL4367@GMAIL.COM</t>
+          <t>RENTERIASANCHEZEMMANUEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>05-03-2026 18:49:34</t>
+          <t>02-03-2026 05:52:47</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2001,21 +1993,29 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>05-03-2026 18:51:30</t>
+          <t>03-03-2026 06:05:34</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>03-03-2026 06:04:45</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2023,11 +2023,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26130522928290004140</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>26130522824140003888</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>ERIKA  RUIZ GONZALEZ</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>549</t>
@@ -2047,12 +2055,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347950</t>
+          <t>348437</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90115</t>
+          <t>90602</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,17 +2070,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OMAR ISAID</t>
+          <t xml:space="preserve">LIZBETH ALEJANDRA </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t xml:space="preserve">ALEGRIA </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2082,28 +2090,28 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6648172166</t>
+          <t>6641235502</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>15-04-2004</t>
+          <t>13-02-1999</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>OISF16483@GMAIL.COM</t>
+          <t>6641235502@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-03-2026 07:29:11</t>
+          <t>04-03-2026 14:06:17</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2128,18 +2136,18 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-03-2026 07:31:02</t>
+          <t>06-03-2026 13:32:33</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -2150,11 +2158,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26130522831810003893</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>26130522949650004189</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Yessica Angulo Barragan</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>899</t>
@@ -2162,24 +2178,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Jose Alfredo Andraca Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348636</t>
+          <t>348317</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90801</t>
+          <t>90482</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2189,27 +2205,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PEDRO</t>
+          <t>RAQUEL ALICIA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VILLANUEVA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>9096424576</t>
+          <t>6645810321</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2219,27 +2235,27 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>11-03-2000</t>
+          <t>25-02-1997</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PEDRO.J1MENEZ1904@GMAIL.COM</t>
+          <t>VILLANUEVA_97@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>05-03-2026 08:52:29</t>
+          <t>04-03-2026 05:38:27</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>borron y cuenta nueva</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2249,17 +2265,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>05-03-2026 08:57:55</t>
+          <t>06-03-2026 06:01:31</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2269,7 +2285,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>05-03-2026 08:56:52</t>
+          <t>06-03-2026 06:00:38</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2279,7 +2295,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2289,14 +2305,22 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26130522911120004098</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>26130522934240004164</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>ERIKA  RUIZ GONZALEZ</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2399,7 +2423,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2440,12 +2464,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348341</t>
+          <t>348319</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90506</t>
+          <t>90484</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2455,17 +2479,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PABLO GAEL</t>
+          <t>CESAR ABRAHAM</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2475,10 +2499,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6644965147</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>6643481788</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PORTICOS</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2486,56 +2514,64 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>14-07-2010</t>
+          <t>29-09-1995</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>VAZQUEZPEREZ862@GMAIL.COM</t>
+          <t>CESAR.MERCADO280@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>04-03-2026 07:57:42</t>
+          <t>04-03-2026 05:43:23</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>borron y cuenta nueva</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>04-03-2026 07:59:00</t>
+          <t>06-03-2026 06:04:20</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>06-03-2026 06:03:51</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2543,36 +2579,44 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26130522874980004010</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>26130522934310004165</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>ERIKA  RUIZ GONZALEZ</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Irving Correa Franco</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348575</t>
+          <t>348341</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90740</t>
+          <t>90506</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2582,17 +2626,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EVA ESTELA</t>
+          <t>PABLO GAEL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ESPARZA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2602,31 +2646,35 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6641111100</t>
+          <t>6644965147</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>27-01-2000</t>
+          <t>14-07-2010</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>EVAESTELAMEDINAESPARZA@GMAIL.COM</t>
+          <t>VAZQUEZPEREZ862@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>04-03-2026 18:44:13</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>04-03-2026 07:57:42</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -2634,28 +2682,28 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>MENSUALIDAD FARMACIAS SIMILARES $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>04-03-2026 18:45:01</t>
+          <t>04-03-2026 07:59:00</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -2666,22 +2714,1090 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26130522895460004065</t>
+          <t>26130522874980004010</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Irving Correa Franco</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>348920</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>91085</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YURIET ALEJANDRA </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CIRA </t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ESTRADA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6634416629</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>10-05-1996</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>CIRAYURIET@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>06-03-2026 14:30:31</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>06-03-2026 14:32:23</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26130522950900004194</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>348575</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>90740</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EVA ESTELA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MEDINA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ESPARZA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6641111100</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>27-01-2000</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>EVAESTELAMEDINAESPARZA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:44:13</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>MENSUALIDAD FARMACIAS SIMILARES $399</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>399</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:45:01</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26130522895460004065</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>347979</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>90144</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA ELENA </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BARRAGAN </t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROMERO </t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3279785050</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTA FE </t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>31-05-1972</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>3279785050@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:56:39</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:04:01</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:03:20</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26130522834330003904</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Jose Alfredo Andraca Rodriguez</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>349255</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>91420</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RUBEN</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>CEJA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>7146231533</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>15-02-1996</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>RUBENCEJAN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>08-03-2026 13:35:21</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>08-03-2026 13:36:34</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>07-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26130522987190004263</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>348636</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>90801</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>JIMENEZ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>9096424576</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>STA FE</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>11-03-2000</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PEDRO.J1MENEZ1904@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>05-03-2026 08:52:29</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>05-03-2026 08:57:55</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>05-03-2026 08:56:52</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26130522911120004098</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>349256</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>91421</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESTELA </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SARIÑANA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>GAMBOA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6641089570</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>STA FE</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>10-05-1992</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>ESTELA.920510@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>08-03-2026 13:42:06</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>08-03-2026 15:21:08</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>08-03-2026 13:47:39</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26130522988330004273</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>ERIKA  RUIZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>348796</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>90961</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAEL ALEJANDRO </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TOPETE</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PANTOJA</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6653472345</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>07-11-2006</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>CERIAL4367@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:49:34</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:51:30</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26130522928290004140</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>348865</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>91030</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>JESUS FRANCISCO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ULLOA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6633241078</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>STA FE</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>06-10-2002</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>CHUY6011@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>06-03-2026 09:36:50</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>06-03-2026 09:41:34</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>06-03-2026 09:41:01</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26130522945810004177</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__SANTA FE.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__SANTA FE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,24 +713,24 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alejandro David  Diaz Quiroga</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>346084</t>
+          <t>343447</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>88249</t>
+          <t>21264</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -740,17 +740,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ADILENE LIZETH</t>
+          <t>GABRIELA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUZMAN </t>
+          <t>ZABAL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARINO </t>
+          <t>VELA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -760,14 +760,10 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6642307004</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>STA FE</t>
-        </is>
-      </c>
+          <t>6641238403</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -775,17 +771,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16-06-1998</t>
+          <t>04-04-1996</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6642307004@GMAIL.COM</t>
+          <t>GABRIELAZABAL11@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>24-02-2026 08:12:15</t>
+          <t>13-02-2026 09:29:18</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -795,44 +791,36 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 07:28:13</t>
+          <t>11-03-2026 09:36:46</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>02-03-2026 07:27:14</t>
-        </is>
-      </c>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -840,44 +828,40 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26130522782370003772</t>
+          <t>26130523084980004502</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yessica Angulo Barragan</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Irving Correa Franco</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347453</t>
+          <t>346084</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89618</t>
+          <t>88249</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -887,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PERLA NARITALY</t>
+          <t>ADILENE LIZETH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t xml:space="preserve">GUZMAN </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t xml:space="preserve">MARINO </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -907,10 +891,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6643090938</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6642307004</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>STA FE</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -918,32 +906,32 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>30-12-1991</t>
+          <t>16-06-1998</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PENANUOS@GMAIL.COM</t>
+          <t>6642307004@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 08:46:02</t>
+          <t>24-02-2026 08:12:15</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -953,7 +941,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 08:47:32</t>
+          <t>02-03-2026 07:28:13</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -961,13 +949,21 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>02-03-2026 07:27:14</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -975,11 +971,19 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26130522784650003780</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26130522782370003772</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Yessica Angulo Barragan</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>549</t>
@@ -987,24 +991,24 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Irving Correa Franco</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347581</t>
+          <t>339520</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89746</t>
+          <t>17338</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1014,17 +1018,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IKER DAVID</t>
+          <t>ERICK HAMED</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DAVILA</t>
+          <t xml:space="preserve"> PARRA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve"> BECERRA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1034,10 +1038,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6643423254</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6641808023</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTA FE </t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1045,32 +1053,32 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>28-01-2010</t>
+          <t>29-06-2007</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>6643423254@GMAIL.COM</t>
+          <t>AMEDBECERRA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 14:06:11</t>
+          <t>30-01-2026 20:49:35</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1080,21 +1088,29 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 14:06:56</t>
+          <t>09-03-2026 18:41:56</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:41:21</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1102,10 +1118,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26130522794110003813</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+          <t>26130523023630004359</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1114,12 +1134,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Alejandro David  Diaz Quiroga</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1293,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347579</t>
+          <t>343446</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89744</t>
+          <t>21263</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,7 +1308,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ARMANDO DAVID</t>
+          <t>GLORIA ISELA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1298,43 +1318,43 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HERMOSILLO</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6633284436</t>
+          <t>8583162926</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>07-09-2010</t>
+          <t>19-04-1991</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6633284436@GMAIL.COM</t>
+          <t>GLORIAIRM19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 13:57:53</t>
+          <t>13-02-2026 09:26:46</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1344,28 +1364,28 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 13:58:56</t>
+          <t>10-03-2026 09:22:06</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1376,19 +1396,23 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26130522793900003812</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+          <t>26130523046650004413</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Alejandro David  Diaz Quiroga</t>
+          <t>Jose Alfredo Andraca Rodriguez</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1400,12 +1424,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347578</t>
+          <t>347453</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89743</t>
+          <t>89618</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1439,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ISSAC RICARDO</t>
+          <t>PERLA NARITALY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,28 +1459,28 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6648285903</t>
+          <t>6643090938</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>30-03-2010</t>
+          <t>30-12-1991</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ISSACRICARDOGARCIA@GMAIL.COM</t>
+          <t>PENANUOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 13:54:20</t>
+          <t>02-03-2026 08:46:02</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1481,7 +1505,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 13:56:23</t>
+          <t>02-03-2026 08:47:32</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1492,7 +1516,7 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1503,7 +1527,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26130522793860003811</t>
+          <t>26130522784650003780</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1515,7 +1539,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Alejandro David  Diaz Quiroga</t>
+          <t>Irving Correa Franco</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1527,12 +1551,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347701</t>
+          <t>347578</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89866</t>
+          <t>89743</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1542,17 +1566,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">MATILDE </t>
+          <t>ISSAC RICARDO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">VELAZQUEZ </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1562,28 +1586,28 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6647329461</t>
+          <t>6648285903</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>14-03-1963</t>
+          <t>30-03-2010</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6647329461@GMAIL.COM</t>
+          <t>ISSACRICARDOGARCIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:06</t>
+          <t>02-03-2026 13:54:20</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1608,7 +1632,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 16:47:21</t>
+          <t>02-03-2026 13:56:23</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1619,7 +1643,7 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1630,7 +1654,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26130522803110003831</t>
+          <t>26130522793860003811</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1642,24 +1666,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alejandro David  Diaz Quiroga</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347983</t>
+          <t>347701</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90148</t>
+          <t>89866</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1669,17 +1693,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CHRISTIAN</t>
+          <t xml:space="preserve">MATILDE </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BENITEZ</t>
+          <t xml:space="preserve">VELAZQUEZ </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1689,28 +1713,28 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6644451633</t>
+          <t>6647329461</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>22-07-2006</t>
+          <t>14-03-1963</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CHISTIANGB563@GMAIL.COM</t>
+          <t>6647329461@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-03-2026 09:06:09</t>
+          <t>02-03-2026 16:46:06</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1735,12 +1759,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 09:10:12</t>
+          <t>02-03-2026 16:47:21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1757,7 +1781,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26130522834480003906</t>
+          <t>26130522803110003831</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1781,12 +1805,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347950</t>
+          <t>347579</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90115</t>
+          <t>89744</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1796,17 +1820,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OMAR ISAID</t>
+          <t>ARMANDO DAVID</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>HERMOSILLO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1816,7 +1840,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6648172166</t>
+          <t>6633284436</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1827,22 +1851,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>15-04-2004</t>
+          <t>07-09-2010</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>OISF16483@GMAIL.COM</t>
+          <t>6633284436@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 07:29:11</t>
+          <t>02-03-2026 13:57:53</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1852,22 +1876,22 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 07:31:02</t>
+          <t>02-03-2026 13:58:56</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1884,19 +1908,19 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26130522831810003893</t>
+          <t>26130522793900003812</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Jose Alfredo Andraca Rodriguez</t>
+          <t>Alejandro David  Diaz Quiroga</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2055,12 +2079,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>348437</t>
+          <t>347581</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90602</t>
+          <t>89746</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2070,17 +2094,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIZBETH ALEJANDRA </t>
+          <t>IKER DAVID</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>DAVILA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEGRIA </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2090,33 +2114,33 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6641235502</t>
+          <t>6643423254</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>13-02-1999</t>
+          <t>28-01-2010</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6641235502@GMAIL.COM</t>
+          <t>6643423254@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>04-03-2026 14:06:17</t>
+          <t>02-03-2026 14:06:11</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2126,28 +2150,28 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>06-03-2026 13:32:33</t>
+          <t>02-03-2026 14:06:56</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -2158,44 +2182,36 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26130522949650004189</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yessica Angulo Barragan</t>
-        </is>
-      </c>
+          <t>26130522794110003813</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alejandro David  Diaz Quiroga</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348317</t>
+          <t>347950</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90482</t>
+          <t>90115</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2205,17 +2221,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>RAQUEL ALICIA</t>
+          <t>OMAR ISAID</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2225,79 +2241,67 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6645810321</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>STA FE</t>
-        </is>
-      </c>
+          <t>6648172166</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>25-02-1997</t>
+          <t>15-04-2004</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>VILLANUEVA_97@HOTMAIL.COM</t>
+          <t>OISF16483@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>04-03-2026 05:38:27</t>
+          <t>03-03-2026 07:29:11</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>borron y cuenta nueva</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>06-03-2026 06:01:31</t>
+          <t>03-03-2026 07:31:02</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>06-03-2026 06:00:38</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2305,44 +2309,36 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26130522934240004164</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>ERIKA  RUIZ GONZALEZ</t>
-        </is>
-      </c>
+          <t>26130522831810003893</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Alfredo Andraca Rodriguez</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>348124</t>
+          <t>347983</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90289</t>
+          <t>90148</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2352,17 +2348,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t>CHRISTIAN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MAR</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PAZ</t>
+          <t>BENITEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2372,7 +2368,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6641690818</t>
+          <t>6644451633</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2383,22 +2379,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>03-09-1997</t>
+          <t>22-07-2006</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>JUAN.MAR@UABC.EDU.MX</t>
+          <t>CHISTIANGB563@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-03-2026 16:35:17</t>
+          <t>03-03-2026 09:06:09</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2408,17 +2404,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 16:36:19</t>
+          <t>03-03-2026 09:10:12</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2429,7 +2425,7 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2440,14 +2436,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26130522847190003941</t>
+          <t>26130522834480003906</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2464,12 +2460,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348319</t>
+          <t>348437</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90484</t>
+          <t>90602</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2479,17 +2475,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CESAR ABRAHAM</t>
+          <t xml:space="preserve">LIZBETH ALEJANDRA </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">ALEGRIA </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2499,57 +2495,53 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6643481788</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>PORTICOS</t>
-        </is>
-      </c>
+          <t>6641235502</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>29-09-1995</t>
+          <t>13-02-1999</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CESAR.MERCADO280@GMAIL.COM</t>
+          <t>6641235502@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>04-03-2026 05:43:23</t>
+          <t>04-03-2026 14:06:17</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>borron y cuenta nueva</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>06-03-2026 06:04:20</t>
+          <t>06-03-2026 13:32:33</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2557,21 +2549,13 @@
           <t>05-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>06-03-2026 06:03:51</t>
-        </is>
-      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2579,7 +2563,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26130522934310004165</t>
+          <t>26130522949650004189</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2589,12 +2573,12 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>ERIKA  RUIZ GONZALEZ</t>
+          <t>Yessica Angulo Barragan</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2611,12 +2595,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348341</t>
+          <t>348124</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90506</t>
+          <t>90289</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2626,17 +2610,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PABLO GAEL</t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve"> MAR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t xml:space="preserve"> PAZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2646,7 +2630,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6644965147</t>
+          <t>6641690818</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2657,22 +2641,22 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>14-07-2010</t>
+          <t>03-09-1997</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>VAZQUEZPEREZ862@GMAIL.COM</t>
+          <t>JUAN.MAR@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>04-03-2026 07:57:42</t>
+          <t>03-03-2026 16:35:17</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2682,22 +2666,22 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>04-03-2026 07:59:00</t>
+          <t>03-03-2026 16:36:19</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2714,36 +2698,36 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26130522874980004010</t>
+          <t>26130522847190003941</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Irving Correa Franco</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348920</t>
+          <t>348319</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>91085</t>
+          <t>90484</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2753,17 +2737,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">YURIET ALEJANDRA </t>
+          <t>CESAR ABRAHAM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CIRA </t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2773,10 +2757,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6634416629</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>6643481788</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>PORTICOS</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2784,42 +2772,42 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>10-05-1996</t>
+          <t>29-09-1995</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CIRAYURIET@GMAIL.COM</t>
+          <t>CESAR.MERCADO280@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>06-03-2026 14:30:31</t>
+          <t>04-03-2026 05:43:23</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>borron y cuenta nueva</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>06-03-2026 14:32:23</t>
+          <t>06-03-2026 06:04:20</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2827,13 +2815,21 @@
           <t>05-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>06-03-2026 06:03:51</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2841,14 +2837,22 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26130522950900004194</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26130522934310004165</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>ERIKA  RUIZ GONZALEZ</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2865,12 +2869,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>348575</t>
+          <t>348341</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90740</t>
+          <t>90506</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2880,17 +2884,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EVA ESTELA</t>
+          <t>PABLO GAEL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ESPARZA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2900,31 +2904,35 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6641111100</t>
+          <t>6644965147</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>27-01-2000</t>
+          <t>14-07-2010</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>EVAESTELAMEDINAESPARZA@GMAIL.COM</t>
+          <t>VAZQUEZPEREZ862@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>04-03-2026 18:44:13</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>04-03-2026 07:57:42</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -2932,17 +2940,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>MENSUALIDAD FARMACIAS SIMILARES $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>04-03-2026 18:45:01</t>
+          <t>04-03-2026 07:59:00</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2953,7 +2961,7 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2964,36 +2972,36 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26130522895460004065</t>
+          <t>26130522874980004010</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Irving Correa Franco</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347979</t>
+          <t>348317</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90144</t>
+          <t>90482</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3003,17 +3011,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA ELENA </t>
+          <t>RAQUEL ALICIA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARRAGAN </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROMERO </t>
+          <t>VILLANUEVA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3023,12 +3031,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3279785050</t>
+          <t>6645810321</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTA FE </t>
+          <t>STA FE</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3038,52 +3046,52 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>31-05-1972</t>
+          <t>25-02-1997</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3279785050@GMAIL.COM</t>
+          <t>VILLANUEVA_97@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>03-03-2026 08:56:39</t>
+          <t>04-03-2026 05:38:27</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>borron y cuenta nueva</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>03-03-2026 09:04:01</t>
+          <t>06-03-2026 06:01:31</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>03-03-2026 09:03:20</t>
+          <t>06-03-2026 06:00:38</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3093,7 +3101,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3103,36 +3111,44 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26130522834330003904</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>26130522934240004164</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>ERIKA  RUIZ GONZALEZ</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Jose Alfredo Andraca Rodriguez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>349255</t>
+          <t>347979</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>91420</t>
+          <t>90144</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3142,87 +3158,99 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>RUBEN</t>
+          <t xml:space="preserve">MARIA ELENA </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CEJA</t>
+          <t xml:space="preserve">BARRAGAN </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>N</t>
+          <t xml:space="preserve">ROMERO </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3279785050</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTA FE </t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>31-05-1972</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>3279785050@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:56:39</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:04:01</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:03:20</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>7146231533</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>15-02-1996</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>RUBENCEJAN@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>08-03-2026 13:35:21</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Sin contrato</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>1 MES $899</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>899</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>08-03-2026 13:36:34</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>07-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3230,36 +3258,36 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26130522987190004263</t>
+          <t>26130522834330003904</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Jose Alfredo Andraca Rodriguez</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>348636</t>
+          <t>348920</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90801</t>
+          <t>91085</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3269,99 +3297,87 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PEDRO</t>
+          <t xml:space="preserve">YURIET ALEJANDRA </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t xml:space="preserve">CIRA </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6634416629</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>10-05-1996</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>CIRAYURIET@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>06-03-2026 14:30:31</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>06-03-2026 14:32:23</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>9096424576</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>STA FE</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>11-03-2000</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>PEDRO.J1MENEZ1904@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>05-03-2026 08:52:29</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Forzoso</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>05-03-2026 08:57:55</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>05-03-2026 08:56:52</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3369,7 +3385,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26130522911120004098</t>
+          <t>26130522950900004194</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3393,12 +3409,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>349256</t>
+          <t>348636</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>91421</t>
+          <t>90801</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3408,27 +3424,27 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESTELA </t>
+          <t>PEDRO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SARIÑANA</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GAMBOA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6641089570</t>
+          <t>9096424576</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3438,57 +3454,57 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>10-05-1992</t>
+          <t>11-03-2000</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ESTELA.920510@HOTMAIL.COM</t>
+          <t>PEDRO.J1MENEZ1904@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>08-03-2026 13:42:06</t>
+          <t>05-03-2026 08:52:29</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>08-03-2026 15:21:08</t>
+          <t>05-03-2026 08:57:55</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>08-03-2026 13:47:39</t>
+          <t>05-03-2026 08:56:52</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3498,7 +3514,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3508,22 +3524,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26130522988330004273</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>ERIKA  RUIZ GONZALEZ</t>
-        </is>
-      </c>
+          <t>26130522911120004098</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3540,12 +3548,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>348796</t>
+          <t>349255</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90961</t>
+          <t>91420</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3555,27 +3563,27 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAEL ALEJANDRO </t>
+          <t>RUBEN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TOPETE</t>
+          <t>CEJA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> PANTOJA</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6653472345</t>
+          <t>7146231533</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3586,22 +3594,22 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>07-11-2006</t>
+          <t>15-02-1996</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CERIAL4367@GMAIL.COM</t>
+          <t>RUBENCEJAN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>05-03-2026 18:49:34</t>
+          <t>08-03-2026 13:35:21</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3611,22 +3619,22 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>05-03-2026 18:51:30</t>
+          <t>08-03-2026 13:36:34</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>07-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3643,14 +3651,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26130522928290004140</t>
+          <t>26130522987190004263</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3667,12 +3675,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>348865</t>
+          <t>349222</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>91030</t>
+          <t>91387</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3682,17 +3690,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>JESUS FRANCISCO</t>
+          <t>GUSTAVO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>AGUIRRE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ULLOA</t>
+          <t>VELAZQUEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3702,12 +3710,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6633241078</t>
+          <t>6648553514</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>STA FE</t>
+          <t>VILLAS TIJUANA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3717,17 +3725,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>06-10-2002</t>
+          <t>24-09-1990</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CHUY6011@GMAIL.COM</t>
+          <t>TAVOAGUIRRE776@GMAAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>06-03-2026 09:36:50</t>
+          <t>08-03-2026 11:57:20</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3752,17 +3760,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>06-03-2026 09:41:34</t>
+          <t>09-03-2026 19:20:24</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>07-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>06-03-2026 09:41:01</t>
+          <t>08-03-2026 11:59:50</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3782,7 +3790,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26130522945810004177</t>
+          <t>26130523026940004368</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3798,6 +3806,4206 @@
         </is>
       </c>
       <c r="AC25" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>349283</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>91448</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BRENDA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PAOLA AYALA AGUILAR</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PAOLA AYALA AGUILAR</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>San Raul</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>31-12-9999</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>brendapayala@icloud.com</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>09-03-2026 05:13:22</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>09-03-2026 05:13:23</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26130522989550004277</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Jose Alfredo Andraca Rodriguez</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>348575</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>90740</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EVA ESTELA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MEDINA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ESPARZA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6641111100</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>27-01-2000</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>EVAESTELAMEDINAESPARZA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:44:13</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>MENSUALIDAD FARMACIAS SIMILARES $399</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:45:01</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26130522895460004065</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>348796</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>90961</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAEL ALEJANDRO </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>TOPETE</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PANTOJA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6653472345</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>07-11-2006</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>CERIAL4367@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:49:34</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:51:30</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26130522928290004140</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>348865</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>91030</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>JESUS FRANCISCO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ULLOA</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6633241078</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>STA FE</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>06-10-2002</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>CHUY6011@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>06-03-2026 09:36:50</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>06-03-2026 09:41:34</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>06-03-2026 09:41:01</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26130522945810004177</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>348972</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>91137</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AIRAM YINGANA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>AGUILAR</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6643155170</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>15-11-2007</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>AIRAMYINGANA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>06-03-2026 16:40:31</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>13-03-2026 16:13:16</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26130523155950004660</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>349256</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>91421</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESTELA </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SARIÑANA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>GAMBOA</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6641089570</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>STA FE</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>10-05-1992</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>ESTELA.920510@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>08-03-2026 13:42:06</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>08-03-2026 15:21:08</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>08-03-2026 13:47:39</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26130522988330004273</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>ERIKA  RUIZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>349327</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>91492</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DIEGO SAUL</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PINEDA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ANDRADE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6645402015</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>27-05-1996</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>DISPA270596@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:47:37</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:49:07</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26130523001060004287</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>349452</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>91617</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>JOSE MARIO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ARMENTA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ANGULO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6681173755</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>29-10-2009</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>JMARMENTAANGULO2009@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:29:05</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:30:51</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26130523009270004321</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>349310</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>91475</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOANA </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PERALTA </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARCIA </t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6648353751</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>05-07-2002</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>6648353751@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:46:32</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>09-03-2026 07:49:11</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26130522999520004281</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>349370</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>91535</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EFREN NICOLAS</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>NIEVES</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6647100058</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>13-12-1993</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>6647100058@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>09-03-2026 11:32:39</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>09-03-2026 11:33:47</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26130523004480004301</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>349827</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>91992</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>HECTOR ALFONSO</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>JIMENEZ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>AVALOS</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6642367602</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>PENDULO</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>30-11-1983</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>6642367602@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>10-03-2026 12:45:23</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>10-03-2026 12:50:25</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>10-03-2026 12:49:53</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26130523050520004425</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>349867</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>92032</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>BRIAN ELI</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> REYES</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> REYES</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6646115971</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>04-12-2008</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>BRIANE.REYES0412@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:09:32</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>10-03-2026 15:11:22</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26130523054410004437</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>350013</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>92178</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ABRAHAM </t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>MOISES</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERNANDEZ </t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6195989637</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>25-08-2005</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>6195989637@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>10-03-2026 20:49:07</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>13-03-2026 16:49:43</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26130523157140004664</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>349423</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>91588</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>XIMENA LIZBETH</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ARIAS</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CISNEROS</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6861862141</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTA FE </t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>30-01-2003</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>XIMENA.ARIASCISNEROS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>09-03-2026 13:37:37</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>11-03-2026 09:02:55</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>11-03-2026 09:02:00</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26130523084220004499</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>350300</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>92464</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>GERARDO</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>POTENCIANO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>RIOS</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6643175917</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>22-02-1994</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6643175917@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>12-03-2026 11:45:42</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>18-03-2026 17:39:19</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26130523299970004984</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>350402</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>92566</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>JORGE ARMANDO</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> DELGADO</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PEREZ</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6611124239</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>17-06-1999</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6611124239@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>12-03-2026 17:33:56</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>12-03-2026 17:35:04</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26130523128760004601</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>349736</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>91901</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE EDUARDO </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SUAZO</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>GUEVARA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6644126104</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>08-02-1991</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>6644126104@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>09-03-2026 21:31:27</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>09-03-2026 21:37:00</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>09-03-2026 21:35:24</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26130523033950004390</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>350982</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>93146</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE ANTONIO </t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6611461401</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTA FE </t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>27-02-1980</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>6611461401@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>16-03-2026 07:53:29</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>16-03-2026 08:00:08</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>16-03-2026 07:59:01</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26130523203800004751</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>351065</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>93229</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CLAUDIA SELENE</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMARILLAS </t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LARA </t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6644098301</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>09-02-1977</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>6644098301@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>16-03-2026 10:15:05</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>16-03-2026 10:22:47</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26130523214560004769</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>350538</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>92702</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>JUAN MANUEL</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>FAJARDO</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>VILLARREAL</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>9612301029</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>09-05-2003</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>FAJARDOVILLAJ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>13-03-2026 10:39:23</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>13-03-2026 10:41:47</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26130523150010004647</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>351021</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>93185</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MARCO ANTONIO</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>BELTRAN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6721189641</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>12-12-2000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>MARCOANTONIOGONZALEZBELTRAN701@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>16-03-2026 09:13:49</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>16-03-2026 09:14:28</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26130523211950004761</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>351062</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>93226</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA ISABEL </t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NUÑEZ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>AMARILLAS</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6642636282</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANTA FE </t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>07-06-1997</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>MARIAISABELAMARILLAS@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>16-03-2026 10:12:14</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>16-03-2026 10:22:47</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>16-03-2026 10:21:17</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26130523214560004769</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>351088</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>93252</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>JONATHAN</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRETADO </t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OLVERA </t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6643080883</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>09-06-2009</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>OLVERAJONATHAN813@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>16-03-2026 11:19:33</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>16-03-2026 11:27:46</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26130523216820004779</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Jose Alfredo Andraca Rodriguez</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>351592</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>93756</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>FRANCO KHALED</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CRUZ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> AVENDAÑO</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6643860729</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>03-01-2009</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>FRANCOKHALEDCRUZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:29:18</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:32:09</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26130523261880004902</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Luis Enrique  Silva Reyna</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>351597</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>93761</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAYRON JADIEL </t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ARRIAGA</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> GARCIA</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>5640027618</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>20-11-2010</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>BAYRONGARCIA823@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:35:21</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:37:35</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26130523262260004905</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Luis Enrique  Silva Reyna</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>351086</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>93250</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRANCISCO ALEXIS </t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OLVERA </t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERNANDEZ </t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>6653927825</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>28-05-1998</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>ALEXISOLV20@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>16-03-2026 11:15:31</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>16-03-2026 11:27:46</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>16-03-2026 11:25:33</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26130523216820004779</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Irving Correa Franco</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>351578</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>93742</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KARLA </t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> NIETO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>6644065035</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>02-05-2001</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NIETOKARLA91@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>17-03-2026 16:49:57</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>17-03-2026 16:59:34</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>17-03-2026 16:58:50</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26130523260080004896</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>351594</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>93758</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>JOSE IGNACIO</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6642560442</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>21-04-1978</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>6642560442@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:30:13</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>17-03-2026 17:32:43</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26130523262000004903</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Luis Enrique  Silva Reyna</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>351070</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>93234</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANDRES IGNACIO </t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>DUEÑAS</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>AMARILLAS</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6647818495</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>15-10-2011</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>647818495@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>16-03-2026 10:28:21</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>16-03-2026 10:30:20</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26130523214790004770</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>351182</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>93346</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JORGE </t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SANTIAGO</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESPINOSA </t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>9622510548</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>STA FE</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>05-01-1998</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>9622510548@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>16-03-2026 13:24:11</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>16-03-2026 13:31:05</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>16-03-2026 13:30:03</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26130523221730004797</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>351425</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>93589</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>MAGALY</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ALTAMIRANO</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>6643987725</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>STA FE</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>24-09-1994</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>MAGALY.ALT.24@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>17-03-2026 08:38:59</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>17-03-2026 08:46:23</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>17-03-2026 08:44:47</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>26130523247310004868</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>352007</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>94171</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>RAUL DE JESUS</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CESEÑA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>6632013652</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>07-09-1989</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>RCESEÑA39@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:34:52</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:45:18</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:42:23</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>26130523310300005006</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>
